--- a/public/downloads/underwriting-demo/sample-deal-summary.xlsx
+++ b/public/downloads/underwriting-demo/sample-deal-summary.xlsx
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>Not stated in the uploaded documents</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>Not stated in the uploaded documents</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>Not stated in the uploaded documents</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
     </row>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Not stated in the uploaded documents</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
     </row>
@@ -18194,7 +18194,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Not stated in the uploaded documents</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -18210,7 +18210,7 @@
       <c r="F28" s="12" t="n"/>
       <c r="G28" s="22" t="inlineStr">
         <is>
-          <t>No uploaded document stated this, so the value reads MISSING. Nothing was assumed to fill it.</t>
+          <t>The internal pipeline pulls a market value by web lookup; the demo does not reach the web.</t>
         </is>
       </c>
     </row>
@@ -18468,7 +18468,7 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Not stated in the uploaded documents</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -18484,7 +18484,7 @@
       <c r="F36" s="12" t="n"/>
       <c r="G36" s="22" t="inlineStr">
         <is>
-          <t>No uploaded document stated this, so the value reads MISSING. Nothing was assumed to fill it.</t>
+          <t>The internal pipeline looks up the attendance-zone elementary, middle and high school and their public ratings; the demo reads a school name only where the memorandum states one and never rates it.</t>
         </is>
       </c>
     </row>
@@ -18501,7 +18501,7 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Not stated in the uploaded documents</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -18517,7 +18517,7 @@
       <c r="F37" s="12" t="n"/>
       <c r="G37" s="22" t="inlineStr">
         <is>
-          <t>No uploaded document stated this, so the value reads MISSING. Nothing was assumed to fill it.</t>
+          <t>The internal pipeline looks up the attendance-zone elementary, middle and high school and their public ratings; the demo reads a school name only where the memorandum states one and never rates it.</t>
         </is>
       </c>
     </row>
@@ -18534,7 +18534,7 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Not stated in the uploaded documents</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -18550,7 +18550,7 @@
       <c r="F38" s="12" t="n"/>
       <c r="G38" s="22" t="inlineStr">
         <is>
-          <t>No uploaded document stated this, so the value reads MISSING. Nothing was assumed to fill it.</t>
+          <t>The internal pipeline looks up the attendance-zone elementary, middle and high school and their public ratings; the demo reads a school name only where the memorandum states one and never rates it.</t>
         </is>
       </c>
     </row>

--- a/public/downloads/underwriting-demo/sample-deal-summary.xlsx
+++ b/public/downloads/underwriting-demo/sample-deal-summary.xlsx
@@ -537,7 +537,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Southern Avenue Sample — as of 2026-08-31</t>
+          <t>505 West — as of 2026-08-31</t>
         </is>
       </c>
     </row>
@@ -575,12 +575,12 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Southern Avenue Sample</t>
+          <t>505 West</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>Illustrative</t>
+          <t>Sample Property Offering Memorandum.pdf — p.3</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Institutional owner-operator (name withheld)</t>
+          <t>Sonoran Residential Holdings LLC</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Sample Property Offering Memorandum.pdf — withheld</t>
+          <t>Illustrative name</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Listing brokerage</t>
+          <t>Desert Ridge Capital Advisors</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>Sample Property Offering Memorandum.pdf — withheld</t>
+          <t>Illustrative name</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>This sample is a real, previously marketed multifamily asset's statements, perturbed: trailing-twelve income lines are 10% higher and expense lines 5% lower than the originals, rent-roll rents are 5% higher and lease dates one month earlier, and the pricing is illustrative. The property facts — unit mix, vintage, size — are the real ones. The ADDRESS is illustrative: 2151 E Southern Ave, Mesa, AZ 85204 is not the asset's location, and the demand, supply, rent-comp and property-tax tabs were pulled for this illustrative address from the same sources a live upload reads. The asset's name, its seller and its brokerage are withheld.</t>
+          <t>This sample is a real, previously marketed multifamily asset's statements, perturbed: trailing-twelve income lines are 10% higher and expense lines 5% lower than the originals, rent-roll rents are 5% higher and lease dates one month earlier, and the pricing is illustrative. The property facts — unit mix, vintage, size — are the real ones. The ADDRESS is illustrative: 2151 E Southern Ave, Mesa, AZ 85204 is not the asset's location, and the demand, supply, rent-comp and property-tax tabs were pulled for this illustrative address from the same sources a live upload reads. The seller and brokerage names are illustrative; the real parties are withheld.</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Southern Avenue Sample — as of 2026-09-03</t>
+          <t>505 West — as of 2026-09-03</t>
         </is>
       </c>
     </row>
@@ -13648,7 +13648,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Southern Avenue Sample — as of 2026-08-31</t>
+          <t>505 West — as of 2026-08-31</t>
         </is>
       </c>
     </row>
@@ -14141,7 +14141,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Southern Avenue Sample — as of 2026-08-31</t>
+          <t>505 West — as of 2026-08-31</t>
         </is>
       </c>
     </row>
@@ -16408,7 +16408,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Southern Avenue Sample — as of 2026-08-31</t>
+          <t>505 West — as of 2026-08-31</t>
         </is>
       </c>
     </row>
@@ -16745,7 +16745,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Southern Avenue Sample — as of 2026-08-31</t>
+          <t>505 West — as of 2026-08-31</t>
         </is>
       </c>
     </row>
@@ -17000,7 +17000,7 @@
       </c>
       <c r="C18" s="22" t="inlineStr">
         <is>
-          <t>This sample is a real, previously marketed multifamily asset's statements, perturbed: trailing-twelve income lines are 10% higher and expense lines 5% lower than the originals, rent-roll rents are 5% higher and lease dates one month earlier, and the pricing is illustrative. The property facts — unit mix, vintage, size — are the real ones. The ADDRESS is illustrative: 2151 E Southern Ave, Mesa, AZ 85204 is not the asset's location, and the demand, supply, rent-comp and property-tax tabs were pulled for this illustrative address from the same sources a live upload reads. The asset's name, its seller and its brokerage are withheld.</t>
+          <t>This sample is a real, previously marketed multifamily asset's statements, perturbed: trailing-twelve income lines are 10% higher and expense lines 5% lower than the originals, rent-roll rents are 5% higher and lease dates one month earlier, and the pricing is illustrative. The property facts — unit mix, vintage, size — are the real ones. The ADDRESS is illustrative: 2151 E Southern Ave, Mesa, AZ 85204 is not the asset's location, and the demand, supply, rent-comp and property-tax tabs were pulled for this illustrative address from the same sources a live upload reads. The seller and brokerage names are illustrative; the real parties are withheld.</t>
         </is>
       </c>
     </row>
@@ -17462,7 +17462,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Southern Avenue Sample — as of 2026-08-31</t>
+          <t>505 West — as of 2026-08-31</t>
         </is>
       </c>
     </row>
@@ -18090,17 +18090,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Southern Avenue Sample</t>
+          <t>505 West</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Illustrative</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>p.3</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -18111,7 +18111,7 @@
       <c r="F25" s="12" t="n"/>
       <c r="G25" s="22" t="inlineStr">
         <is>
-          <t>The sample's name is illustrative; the asset's real name is withheld.</t>
+          <t>The deal name as the memorandum states it.</t>
         </is>
       </c>
     </row>
@@ -18259,17 +18259,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Listing brokerage</t>
+          <t>Desert Ridge Capital Advisors</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
+          <t>Illustrative name</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>withheld</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -18280,7 +18280,7 @@
       <c r="F30" s="12" t="n"/>
       <c r="G30" s="22" t="inlineStr">
         <is>
-          <t>Stated in the memorandum; withheld from the public sample because it identifies the real asset.</t>
+          <t>An illustrative name. The real party is withheld from the public sample.</t>
         </is>
       </c>
     </row>
@@ -18562,17 +18562,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Institutional owner-operator (name withheld)</t>
+          <t>Sonoran Residential Holdings LLC</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
+          <t>Illustrative name</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>withheld</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -18583,7 +18583,7 @@
       <c r="F39" s="12" t="n"/>
       <c r="G39" s="22" t="inlineStr">
         <is>
-          <t>Stated in the memorandum; withheld from the public sample because it identifies the real asset.</t>
+          <t>An illustrative name. The real party is withheld from the public sample.</t>
         </is>
       </c>
     </row>

--- a/public/downloads/underwriting-demo/sample-deal-summary.xlsx
+++ b/public/downloads/underwriting-demo/sample-deal-summary.xlsx
@@ -1377,17 +1377,12 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>The internal pipeline looks up the attendance-zone elementary, middle and high school and their public ratings; the demo reads a school name only where the memorandum states one and never rates it.</t>
+          <t>Porter Elementary School</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Internal underwriting agent — attendance-zone school lookup — 2151 E Southern Ave, Mesa, AZ 85204 on 2026-09-14</t>
         </is>
       </c>
     </row>
@@ -1397,15 +1392,8 @@
           <t>Elementary rating</t>
         </is>
       </c>
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>Internal pipeline only</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>The internal pipeline looks up the attendance-zone elementary, middle and high school and their public ratings; the demo reads a school name only where the memorandum states one and never rates it.</t>
-        </is>
+      <c r="B66" s="8" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="67">
@@ -1416,17 +1404,12 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
-        </is>
-      </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>The internal pipeline looks up the attendance-zone elementary, middle and high school and their public ratings; the demo reads a school name only where the memorandum states one and never rates it.</t>
+          <t>Taylor Junior High School</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Internal underwriting agent — attendance-zone school lookup — 2151 E Southern Ave, Mesa, AZ 85204 on 2026-09-14</t>
         </is>
       </c>
     </row>
@@ -1436,15 +1419,8 @@
           <t>Middle rating</t>
         </is>
       </c>
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>Internal pipeline only</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>The internal pipeline looks up the attendance-zone elementary, middle and high school and their public ratings; the demo reads a school name only where the memorandum states one and never rates it.</t>
-        </is>
+      <c r="B68" s="8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -1455,17 +1431,12 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>The internal pipeline looks up the attendance-zone elementary, middle and high school and their public ratings; the demo reads a school name only where the memorandum states one and never rates it.</t>
+          <t>Mesa High School</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Internal underwriting agent — attendance-zone school lookup — 2151 E Southern Ave, Mesa, AZ 85204 on 2026-09-14</t>
         </is>
       </c>
     </row>
@@ -1475,15 +1446,8 @@
           <t>High rating</t>
         </is>
       </c>
-      <c r="B70" s="5" t="inlineStr">
-        <is>
-          <t>Internal pipeline only</t>
-        </is>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>The internal pipeline looks up the attendance-zone elementary, middle and high school and their public ratings; the demo reads a school name only where the memorandum states one and never rates it.</t>
-        </is>
+      <c r="B70" s="8" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="72">
@@ -1503,7 +1467,7 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>This sample is a real, previously marketed multifamily asset's statements, perturbed: trailing-twelve income lines are 10% higher and expense lines 5% lower than the originals, rent-roll rents are 5% higher and lease dates one month earlier, and the pricing is illustrative. The property facts — unit mix, vintage, size — are the real ones. The ADDRESS is illustrative: 2151 E Southern Ave, Mesa, AZ 85204 is not the asset's location, and the demand, supply, rent-comp and property-tax tabs were pulled for this illustrative address from the same sources a live upload reads. The seller and brokerage names are illustrative; the real parties are withheld.</t>
+          <t>The address shown is illustrative and is not the asset's location; the demand, supply, rent-comp and property-tax tabs were pulled for this illustrative address from the same sources a live upload reads. The seller and brokerage names are illustrative; the real parties are withheld. Pricing is illustrative.</t>
         </is>
       </c>
     </row>
@@ -16990,7 +16954,7 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>This sample is a real deal, perturbed, at an illustrative address</t>
+          <t>This sample sits at an illustrative address</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -17000,7 +16964,7 @@
       </c>
       <c r="C18" s="22" t="inlineStr">
         <is>
-          <t>This sample is a real, previously marketed multifamily asset's statements, perturbed: trailing-twelve income lines are 10% higher and expense lines 5% lower than the originals, rent-roll rents are 5% higher and lease dates one month earlier, and the pricing is illustrative. The property facts — unit mix, vintage, size — are the real ones. The ADDRESS is illustrative: 2151 E Southern Ave, Mesa, AZ 85204 is not the asset's location, and the demand, supply, rent-comp and property-tax tabs were pulled for this illustrative address from the same sources a live upload reads. The seller and brokerage names are illustrative; the real parties are withheld.</t>
+          <t>The address shown is illustrative and is not the asset's location; the demand, supply, rent-comp and property-tax tabs were pulled for this illustrative address from the same sources a live upload reads. The seller and brokerage names are illustrative; the real parties are withheld. Pricing is illustrative.</t>
         </is>
       </c>
     </row>
@@ -18463,17 +18427,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>Porter Elementary School</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Internal underwriting agent — attendance-zone school lookup</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2151 E Southern Ave, Mesa, AZ 85204 on 2026-09-14</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -18484,7 +18448,7 @@
       <c r="F36" s="12" t="n"/>
       <c r="G36" s="22" t="inlineStr">
         <is>
-          <t>The internal pipeline looks up the attendance-zone elementary, middle and high school and their public ratings; the demo reads a school name only where the memorandum states one and never rates it.</t>
+          <t>Looked up for the illustrative address by the internal underwriting agent; the public demo does not run this on an uploaded deal.</t>
         </is>
       </c>
     </row>
@@ -18496,17 +18460,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>Mesa High School</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Internal underwriting agent — attendance-zone school lookup</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2151 E Southern Ave, Mesa, AZ 85204 on 2026-09-14</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -18517,7 +18481,7 @@
       <c r="F37" s="12" t="n"/>
       <c r="G37" s="22" t="inlineStr">
         <is>
-          <t>The internal pipeline looks up the attendance-zone elementary, middle and high school and their public ratings; the demo reads a school name only where the memorandum states one and never rates it.</t>
+          <t>Looked up for the illustrative address by the internal underwriting agent; the public demo does not run this on an uploaded deal.</t>
         </is>
       </c>
     </row>
@@ -18529,17 +18493,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>Taylor Junior High School</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Internal underwriting agent — attendance-zone school lookup</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2151 E Southern Ave, Mesa, AZ 85204 on 2026-09-14</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -18550,7 +18514,7 @@
       <c r="F38" s="12" t="n"/>
       <c r="G38" s="22" t="inlineStr">
         <is>
-          <t>The internal pipeline looks up the attendance-zone elementary, middle and high school and their public ratings; the demo reads a school name only where the memorandum states one and never rates it.</t>
+          <t>Looked up for the illustrative address by the internal underwriting agent; the public demo does not run this on an uploaded deal.</t>
         </is>
       </c>
     </row>

--- a/public/downloads/underwriting-demo/sample-deal-summary.xlsx
+++ b/public/downloads/underwriting-demo/sample-deal-summary.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>garden-style multifamily</t>
+          <t>Garden-style multifamily</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>One-, two-, and three-bedroom residences averaging 856 square feet across 40 buildings on 15.87 acres</t>
+          <t>Diversified mix of one-, two-, and three-bedroom residences averaging 856 square feet on approximately 15.9 acres</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -18359,7 +18359,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>One-, two-, and three-bedroom residences averaging 856 square feet across 40 buildings …</t>
+          <t>Diversified mix of one-, two-, and three-bedroom residences averaging 856 square feet o…</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -18394,7 +18394,7 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>garden-style multifamily</t>
+          <t>Garden-style multifamily</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">

--- a/public/downloads/underwriting-demo/sample-deal-summary.xlsx
+++ b/public/downloads/underwriting-demo/sample-deal-summary.xlsx
@@ -1052,7 +1052,7 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>New-lease average where the plan has new leases in the lookback window, otherwise in-place. Never a blend of new and renewal.</t>
+          <t>New move-in rent (residents who moved in inside the lookback window, by move-in date) where the plan has one, otherwise in-place (in-place outright when the roll has no usable lease start or move-in date). Never a blend of new and renewal.</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="C11" s="22" t="inlineStr">
         <is>
-          <t>Market rent for the model is the new-lease average where a plan has new leases inside the lookback window, and in-place rent where it does not. It is never the average of new and renewal leases together. A blended figure reads as market rent and is not one: renewals are priced off the existing rent, so blending them in drags the number toward where rents used to be and understates the gap the underwriting is trying to measure. On an asset whose in-place rents sit above what the market is currently signing, the rule produces a market rent BELOW in-place — which is the correct and uncomfortable answer, and the one a blend would hide.</t>
+          <t>Market rent for the model is the new move-in rent — residents whose move-in date falls inside the lookback window, whatever their lease type — where a plan has one, and in-place rent where it does not. It is never the average of every lease signed, new and renewal together. A blended figure reads as market rent and is not one: renewals are priced off the existing rent, so blending them in drags the number toward where rents used to be and understates the gap the underwriting is trying to measure. On an asset whose in-place rents sit above what the market is currently signing, the rule produces a market rent BELOW in-place — which is the correct and uncomfortable answer, and the one a blend would hide.</t>
         </is>
       </c>
     </row>
@@ -8744,7 +8744,7 @@
       </c>
       <c r="C43" s="22" t="inlineStr">
         <is>
-          <t>The uploaded rent roll stated the PERIOD it covers rather than a day: as-of taken as 2026-08-31, the last day of the stated period 202608. Every window on this page (the new-lease lookback and annualised turnover) is measured back from that date, not from the day of the upload.</t>
+          <t>The uploaded rent roll stated the PERIOD it covers rather than a day: as-of taken as 2026-08-31, the last day of the stated period 202608. Every window on this page (the move-in and lease-signed lookback, and annualised turnover) is measured back from that date, not from the day of the upload.</t>
         </is>
       </c>
     </row>

--- a/public/downloads/underwriting-demo/sample-deal-summary.xlsx
+++ b/public/downloads/underwriting-demo/sample-deal-summary.xlsx
@@ -3502,7 +3502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I106"/>
+  <dimension ref="A1:I107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -4610,139 +4610,124 @@
         <v>-0.1242759499897198</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Home values: Zillow Home Value Index (ZHVI), Zillow Group</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
         <is>
           <t>Labor market</t>
         </is>
       </c>
-      <c r="B57" s="4" t="n"/>
-      <c r="C57" s="4" t="n"/>
-      <c r="D57" s="4" t="n"/>
-      <c r="E57" s="4" t="n"/>
-      <c r="F57" s="4" t="n"/>
-      <c r="G57" s="4" t="n"/>
-      <c r="H57" s="4" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="6" t="inlineStr">
+      <c r="B58" s="4" t="n"/>
+      <c r="C58" s="4" t="n"/>
+      <c r="D58" s="4" t="n"/>
+      <c r="E58" s="4" t="n"/>
+      <c r="F58" s="4" t="n"/>
+      <c r="G58" s="4" t="n"/>
+      <c r="H58" s="4" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>Ring job counts are WORKPLACE counts — jobs located inside the ring, not residents who hold jobs. The unemployment row above is the opposite: residents. The two answer different questions and are not interchangeable.</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="14" t="inlineStr"/>
-      <c r="B59" s="14" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="14" t="inlineStr"/>
+      <c r="B60" s="14" t="inlineStr">
         <is>
           <t>1 mi</t>
         </is>
       </c>
-      <c r="C59" s="14" t="inlineStr">
+      <c r="C60" s="14" t="inlineStr">
         <is>
           <t>3 mi</t>
         </is>
       </c>
-      <c r="D59" s="14" t="inlineStr">
+      <c r="D60" s="14" t="inlineStr">
         <is>
           <t>5 mi</t>
         </is>
       </c>
-      <c r="E59" s="14" t="inlineStr">
+      <c r="E60" s="14" t="inlineStr">
         <is>
           <t>10 mi</t>
         </is>
       </c>
-      <c r="F59" s="14" t="inlineStr">
+      <c r="F60" s="14" t="inlineStr">
         <is>
           <t>Phoenix MSA</t>
         </is>
       </c>
-      <c r="G59" s="14" t="inlineStr">
+      <c r="G60" s="14" t="inlineStr">
         <is>
           <t>Arizona</t>
         </is>
       </c>
-      <c r="H59" s="14" t="inlineStr">
+      <c r="H60" s="14" t="inlineStr">
         <is>
           <t>U.S.</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t>Unemployment rate (residents, ACS)</t>
         </is>
       </c>
-      <c r="B60" s="11" t="n">
+      <c r="B61" s="11" t="n">
         <v>0.052</v>
       </c>
-      <c r="C60" s="11" t="n">
+      <c r="C61" s="11" t="n">
         <v>0.046</v>
       </c>
-      <c r="D60" s="11" t="n">
+      <c r="D61" s="11" t="n">
         <v>0.045</v>
       </c>
-      <c r="E60" s="11" t="n">
+      <c r="E61" s="11" t="n">
         <v>0.043</v>
       </c>
-      <c r="F60" s="11" t="n">
+      <c r="F61" s="11" t="n">
         <v>0.047</v>
       </c>
-      <c r="G60" s="11" t="n">
+      <c r="G61" s="11" t="n">
         <v>0.051</v>
       </c>
-      <c r="H60" s="11" t="n">
+      <c r="H61" s="11" t="n">
         <v>0.052</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="13" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="13" t="inlineStr">
         <is>
           <t>Jobs located inside the ring — LODES workplace counts</t>
         </is>
       </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    2019</t>
-        </is>
-      </c>
-      <c r="B62" s="7" t="n">
-        <v>4140</v>
-      </c>
-      <c r="C62" s="7" t="n">
-        <v>59139</v>
-      </c>
-      <c r="D62" s="7" t="n">
-        <v>150089</v>
-      </c>
-      <c r="E62" s="7" t="n">
-        <v>458614</v>
-      </c>
-      <c r="F62" s="12" t="n"/>
-      <c r="G62" s="12" t="n"/>
-      <c r="H62" s="12" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    2020</t>
+          <t xml:space="preserve">    2019</t>
         </is>
       </c>
       <c r="B63" s="7" t="n">
-        <v>4549</v>
+        <v>4140</v>
       </c>
       <c r="C63" s="7" t="n">
-        <v>58261</v>
+        <v>59139</v>
       </c>
       <c r="D63" s="7" t="n">
-        <v>150082</v>
+        <v>150089</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>455835</v>
+        <v>458614</v>
       </c>
       <c r="F63" s="12" t="n"/>
       <c r="G63" s="12" t="n"/>
@@ -4751,20 +4736,20 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    2021</t>
+          <t xml:space="preserve">    2020</t>
         </is>
       </c>
       <c r="B64" s="7" t="n">
-        <v>4552</v>
+        <v>4549</v>
       </c>
       <c r="C64" s="7" t="n">
-        <v>59079</v>
+        <v>58261</v>
       </c>
       <c r="D64" s="7" t="n">
-        <v>152118</v>
+        <v>150082</v>
       </c>
       <c r="E64" s="7" t="n">
-        <v>466392</v>
+        <v>455835</v>
       </c>
       <c r="F64" s="12" t="n"/>
       <c r="G64" s="12" t="n"/>
@@ -4773,20 +4758,20 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    2022</t>
+          <t xml:space="preserve">    2021</t>
         </is>
       </c>
       <c r="B65" s="7" t="n">
-        <v>4741</v>
+        <v>4552</v>
       </c>
       <c r="C65" s="7" t="n">
-        <v>63403</v>
+        <v>59079</v>
       </c>
       <c r="D65" s="7" t="n">
-        <v>162056</v>
+        <v>152118</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>501214</v>
+        <v>466392</v>
       </c>
       <c r="F65" s="12" t="n"/>
       <c r="G65" s="12" t="n"/>
@@ -4795,20 +4780,20 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    2023  (latest)</t>
+          <t xml:space="preserve">    2022</t>
         </is>
       </c>
       <c r="B66" s="7" t="n">
-        <v>5239</v>
+        <v>4741</v>
       </c>
       <c r="C66" s="7" t="n">
-        <v>65083</v>
+        <v>63403</v>
       </c>
       <c r="D66" s="7" t="n">
-        <v>165142</v>
+        <v>162056</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>516916</v>
+        <v>501214</v>
       </c>
       <c r="F66" s="12" t="n"/>
       <c r="G66" s="12" t="n"/>
@@ -4817,947 +4802,969 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Job growth 2019 to 2023</t>
-        </is>
-      </c>
-      <c r="B67" s="11" t="n">
-        <v>0.2654589371980676</v>
-      </c>
-      <c r="C67" s="11" t="n">
-        <v>0.1005089703917887</v>
-      </c>
-      <c r="D67" s="11" t="n">
-        <v>0.1002938256634396</v>
-      </c>
-      <c r="E67" s="11" t="n">
-        <v>0.1271265159807595</v>
+          <t xml:space="preserve">    2023  (latest)</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="n">
+        <v>5239</v>
+      </c>
+      <c r="C67" s="7" t="n">
+        <v>65083</v>
+      </c>
+      <c r="D67" s="7" t="n">
+        <v>165142</v>
+      </c>
+      <c r="E67" s="7" t="n">
+        <v>516916</v>
       </c>
       <c r="F67" s="12" t="n"/>
       <c r="G67" s="12" t="n"/>
       <c r="H67" s="12" t="n"/>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>Already a fraction in the engine's output, unlike the rates above.</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Job CAGR (4-yr)</t>
+          <t xml:space="preserve">    Job growth 2019 to 2023</t>
         </is>
       </c>
       <c r="B68" s="11" t="n">
-        <v>0.06062537773196808</v>
+        <v>0.2654589371980676</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>0.02423213297708893</v>
+        <v>0.1005089703917887</v>
       </c>
       <c r="D68" s="11" t="n">
-        <v>0.02418207107245318</v>
+        <v>0.1002938256634396</v>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.03036990821614882</v>
+        <v>0.1271265159807595</v>
       </c>
       <c r="F68" s="12" t="n"/>
       <c r="G68" s="12" t="n"/>
       <c r="H68" s="12" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="13" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>Already a fraction in the engine's output, unlike the rates above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Job CAGR (4-yr)</t>
+        </is>
+      </c>
+      <c r="B69" s="11" t="n">
+        <v>0.06062537773196808</v>
+      </c>
+      <c r="C69" s="11" t="n">
+        <v>0.02423213297708893</v>
+      </c>
+      <c r="D69" s="11" t="n">
+        <v>0.02418207107245318</v>
+      </c>
+      <c r="E69" s="11" t="n">
+        <v>0.03036990821614882</v>
+      </c>
+      <c r="F69" s="12" t="n"/>
+      <c r="G69" s="12" t="n"/>
+      <c r="H69" s="12" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="13" t="inlineStr">
         <is>
           <t>Metro nonfarm employment and unemployment — Maricopa County, Arizona</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="14" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="14" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B71" s="14" t="inlineStr">
+      <c r="B72" s="14" t="inlineStr">
         <is>
           <t>Nonfarm jobs (000s)</t>
         </is>
       </c>
-      <c r="C71" s="14" t="inlineStr">
+      <c r="C72" s="14" t="inlineStr">
         <is>
           <t>Job growth</t>
         </is>
       </c>
-      <c r="D71" s="14" t="inlineStr">
+      <c r="D72" s="14" t="inlineStr">
         <is>
           <t>Unemployment</t>
         </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="12" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B72" s="10" t="n">
-        <v>2469.37</v>
-      </c>
-      <c r="C72" s="11" t="n">
-        <v>0.002793919975309533</v>
-      </c>
-      <c r="D72" s="11" t="n">
-        <v>0.0431</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="12" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B73" s="10" t="n">
-        <v>2462.49</v>
+        <v>2469.37</v>
       </c>
       <c r="C73" s="11" t="n">
-        <v>0.002626178726730766</v>
+        <v>0.002793919975309533</v>
       </c>
       <c r="D73" s="11" t="n">
-        <v>0.0381</v>
+        <v>0.0431</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="12" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B74" s="10" t="n">
-        <v>2456.04</v>
+        <v>2462.49</v>
       </c>
       <c r="C74" s="11" t="n">
-        <v>0.02243406947942472</v>
+        <v>0.002626178726730766</v>
       </c>
       <c r="D74" s="11" t="n">
-        <v>0.0328</v>
+        <v>0.0381</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="12" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B75" s="10" t="n">
-        <v>2402.15</v>
+        <v>2456.04</v>
       </c>
       <c r="C75" s="11" t="n">
-        <v>0.03166081866321946</v>
+        <v>0.02243406947942472</v>
       </c>
       <c r="D75" s="11" t="n">
-        <v>0.0326</v>
+        <v>0.0328</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="12" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B76" s="10" t="n">
-        <v>2328.43</v>
+        <v>2402.15</v>
       </c>
       <c r="C76" s="11" t="n">
-        <v>0.05041323059710923</v>
+        <v>0.03166081866321946</v>
       </c>
       <c r="D76" s="11" t="n">
-        <v>0.0332</v>
+        <v>0.0326</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="12" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B77" s="10" t="n">
-        <v>2216.68</v>
+        <v>2328.43</v>
       </c>
       <c r="C77" s="11" t="n">
-        <v>0.04558897751446889</v>
+        <v>0.05041323059710923</v>
       </c>
       <c r="D77" s="11" t="n">
-        <v>0.0462</v>
+        <v>0.0332</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="12" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B78" s="10" t="n">
-        <v>2120.03</v>
+        <v>2216.68</v>
       </c>
       <c r="C78" s="11" t="n">
-        <v>-0.02628980328576602</v>
+        <v>0.04558897751446889</v>
       </c>
       <c r="D78" s="11" t="n">
-        <v>0.0728</v>
+        <v>0.0462</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="12" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B79" s="10" t="n">
-        <v>2177.27</v>
+        <v>2120.03</v>
       </c>
       <c r="C79" s="11" t="n">
-        <v>0.03380213477170857</v>
+        <v>-0.02628980328576602</v>
       </c>
       <c r="D79" s="11" t="n">
-        <v>0.0413</v>
+        <v>0.0728</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="12" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B80" s="10" t="n">
-        <v>2106.08</v>
+        <v>2177.27</v>
       </c>
       <c r="C80" s="11" t="n">
-        <v>0.03344079531681654</v>
+        <v>0.03380213477170857</v>
       </c>
       <c r="D80" s="11" t="n">
-        <v>0.0415</v>
+        <v>0.0413</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="12" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B81" s="10" t="n">
-        <v>2037.93</v>
+        <v>2106.08</v>
       </c>
       <c r="C81" s="11" t="n">
-        <v>0.03009517840264042</v>
+        <v>0.03344079531681654</v>
       </c>
       <c r="D81" s="11" t="n">
-        <v>0.0428</v>
+        <v>0.0415</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="12" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B82" s="10" t="n">
+        <v>2037.93</v>
+      </c>
+      <c r="C82" s="11" t="n">
+        <v>0.03009517840264042</v>
+      </c>
+      <c r="D82" s="11" t="n">
+        <v>0.0428</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="12" t="n">
         <v>2016</v>
       </c>
-      <c r="B82" s="10" t="n">
+      <c r="B83" s="10" t="n">
         <v>1978.39</v>
       </c>
-      <c r="C82" s="12" t="n"/>
-      <c r="D82" s="11" t="n">
+      <c r="C83" s="12" t="n"/>
+      <c r="D83" s="11" t="n">
         <v>0.0471</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="4" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
         <is>
           <t>Jobs by industry (2023)</t>
         </is>
       </c>
-      <c r="B84" s="4" t="n"/>
-      <c r="C84" s="4" t="n"/>
-      <c r="D84" s="4" t="n"/>
-      <c r="E84" s="4" t="n"/>
-      <c r="F84" s="4" t="n"/>
-      <c r="G84" s="4" t="n"/>
-      <c r="H84" s="4" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="6" t="inlineStr">
+      <c r="B85" s="4" t="n"/>
+      <c r="C85" s="4" t="n"/>
+      <c r="D85" s="4" t="n"/>
+      <c r="E85" s="4" t="n"/>
+      <c r="F85" s="4" t="n"/>
+      <c r="G85" s="4" t="n"/>
+      <c r="H85" s="4" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
         <is>
           <t>Share of jobs by sector, sorted by the metro's own concentration. Ring, MSA and state shares come from LODES workplace counts; the U.S. column is QCEW — a different survey, so read it as a benchmark rather than the same measurement. The location quotient on each row is the metro share over the national share.</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="14" t="inlineStr"/>
-      <c r="B86" s="14" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="14" t="inlineStr"/>
+      <c r="B87" s="14" t="inlineStr">
         <is>
           <t>1 mi</t>
         </is>
       </c>
-      <c r="C86" s="14" t="inlineStr">
+      <c r="C87" s="14" t="inlineStr">
         <is>
           <t>3 mi</t>
         </is>
       </c>
-      <c r="D86" s="14" t="inlineStr">
+      <c r="D87" s="14" t="inlineStr">
         <is>
           <t>5 mi</t>
         </is>
       </c>
-      <c r="E86" s="14" t="inlineStr">
+      <c r="E87" s="14" t="inlineStr">
         <is>
           <t>10 mi</t>
         </is>
       </c>
-      <c r="F86" s="14" t="inlineStr">
+      <c r="F87" s="14" t="inlineStr">
         <is>
           <t>Phoenix MSA</t>
         </is>
       </c>
-      <c r="G86" s="14" t="inlineStr">
+      <c r="G87" s="14" t="inlineStr">
         <is>
           <t>Arizona</t>
         </is>
       </c>
-      <c r="H86" s="14" t="inlineStr">
+      <c r="H87" s="14" t="inlineStr">
         <is>
           <t>U.S.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="5" t="inlineStr">
-        <is>
-          <t>Health Care/Social Asst</t>
-        </is>
-      </c>
-      <c r="B87" s="11" t="n">
-        <v>0.1675892345867532</v>
-      </c>
-      <c r="C87" s="11" t="n">
-        <v>0.1324022003011585</v>
-      </c>
-      <c r="D87" s="11" t="n">
-        <v>0.128294871717239</v>
-      </c>
-      <c r="E87" s="11" t="n">
-        <v>0.1575223875399726</v>
-      </c>
-      <c r="F87" s="11" t="n">
-        <v>0.1439230188830762</v>
-      </c>
-      <c r="G87" s="11" t="n">
-        <v>0.1480747084992491</v>
-      </c>
-      <c r="H87" s="11" t="n">
-        <v>0.1524112221376376</v>
-      </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>Location quotient vs U.S.: 0.94x — less concentrated here.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>Retail Trade</t>
+          <t>Health Care/Social Asst</t>
         </is>
       </c>
       <c r="B88" s="11" t="n">
-        <v>0.1402939492269517</v>
+        <v>0.1675892345867532</v>
       </c>
       <c r="C88" s="11" t="n">
-        <v>0.1312959036292677</v>
+        <v>0.1324022003011585</v>
       </c>
       <c r="D88" s="11" t="n">
-        <v>0.1295604415567115</v>
+        <v>0.128294871717239</v>
       </c>
       <c r="E88" s="11" t="n">
-        <v>0.1260357078602561</v>
+        <v>0.1575223875399726</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>0.1090536545703669</v>
+        <v>0.1439230188830762</v>
       </c>
       <c r="G88" s="11" t="n">
-        <v>0.1100206596769526</v>
+        <v>0.1480747084992491</v>
       </c>
       <c r="H88" s="11" t="n">
-        <v>0.1019921721752688</v>
+        <v>0.1524112221376376</v>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>Location quotient vs U.S.: 1.07x — more concentrated here.</t>
+          <t>Location quotient vs U.S.: 0.94x — less concentrated here.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>Accommodation/Food Svcs</t>
+          <t>Retail Trade</t>
         </is>
       </c>
       <c r="B89" s="11" t="n">
-        <v>0.1093720175606032</v>
+        <v>0.1402939492269517</v>
       </c>
       <c r="C89" s="11" t="n">
-        <v>0.09160751052518361</v>
+        <v>0.1312959036292677</v>
       </c>
       <c r="D89" s="11" t="n">
-        <v>0.09612275421907074</v>
+        <v>0.1295604415567115</v>
       </c>
       <c r="E89" s="11" t="n">
-        <v>0.0974934080326242</v>
+        <v>0.1260357078602561</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>0.09153364975214603</v>
+        <v>0.1090536545703669</v>
       </c>
       <c r="G89" s="11" t="n">
-        <v>0.09799831322286184</v>
+        <v>0.1100206596769526</v>
       </c>
       <c r="H89" s="11" t="n">
-        <v>0.09210003364899073</v>
+        <v>0.1019921721752688</v>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>Location quotient vs U.S.: 0.99x — less concentrated here.</t>
+          <t>Location quotient vs U.S.: 1.07x — more concentrated here.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>Admin/Support/Waste</t>
+          <t>Accommodation/Food Svcs</t>
         </is>
       </c>
       <c r="B90" s="11" t="n">
-        <v>0.09200229051345676</v>
+        <v>0.1093720175606032</v>
       </c>
       <c r="C90" s="11" t="n">
-        <v>0.1102148059371255</v>
+        <v>0.09160751052518361</v>
       </c>
       <c r="D90" s="11" t="n">
-        <v>0.09007950685163767</v>
+        <v>0.09612275421907074</v>
       </c>
       <c r="E90" s="11" t="n">
-        <v>0.07061675278623067</v>
+        <v>0.0974934080326242</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>0.08654896600644772</v>
+        <v>0.09153364975214603</v>
       </c>
       <c r="G90" s="11" t="n">
-        <v>0.08053357937738248</v>
+        <v>0.09799831322286184</v>
       </c>
       <c r="H90" s="11" t="n">
-        <v>0.06170694540515537</v>
+        <v>0.09210003364899073</v>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>Location quotient vs U.S.: 1.40x — more concentrated here.</t>
+          <t>Location quotient vs U.S.: 0.99x — less concentrated here.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Admin/Support/Waste</t>
         </is>
       </c>
       <c r="B91" s="11" t="n">
-        <v>0.03397594960870395</v>
+        <v>0.09200229051345676</v>
       </c>
       <c r="C91" s="11" t="n">
-        <v>0.1437571064195937</v>
+        <v>0.1102148059371255</v>
       </c>
       <c r="D91" s="11" t="n">
-        <v>0.1065198040486124</v>
+        <v>0.09007950685163767</v>
       </c>
       <c r="E91" s="11" t="n">
-        <v>0.07423822393150158</v>
+        <v>0.07061675278623067</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>0.07168567465967132</v>
+        <v>0.08654896600644772</v>
       </c>
       <c r="G91" s="11" t="n">
-        <v>0.0692629280579044</v>
+        <v>0.08053357937738248</v>
       </c>
       <c r="H91" s="11" t="n">
-        <v>0.0531750429082045</v>
+        <v>0.06170694540515537</v>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>Location quotient vs U.S.: 1.35x — more concentrated here.</t>
+          <t>Location quotient vs U.S.: 1.40x — more concentrated here.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>Educational Services</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="B92" s="11" t="n">
-        <v>0.05630845581217789</v>
+        <v>0.03397594960870395</v>
       </c>
       <c r="C92" s="11" t="n">
-        <v>0.09185335423004824</v>
+        <v>0.1437571064195937</v>
       </c>
       <c r="D92" s="11" t="n">
-        <v>0.1103528457155314</v>
+        <v>0.1065198040486124</v>
       </c>
       <c r="E92" s="11" t="n">
-        <v>0.09778359001541834</v>
+        <v>0.07423822393150158</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>0.0692937123890178</v>
+        <v>0.07168567465967132</v>
       </c>
       <c r="G92" s="11" t="n">
-        <v>0.07805244418719343</v>
+        <v>0.0692629280579044</v>
       </c>
       <c r="H92" s="11" t="n">
-        <v>0.08463384936674581</v>
+        <v>0.0531750429082045</v>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>Location quotient vs U.S.: 0.82x — less concentrated here.</t>
+          <t>Location quotient vs U.S.: 1.35x — more concentrated here.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>Finance/Insurance</t>
+          <t>Educational Services</t>
         </is>
       </c>
       <c r="B93" s="11" t="n">
-        <v>0.01355220461920214</v>
+        <v>0.05630845581217789</v>
       </c>
       <c r="C93" s="11" t="n">
-        <v>0.02564457146369196</v>
+        <v>0.09185335423004824</v>
       </c>
       <c r="D93" s="11" t="n">
-        <v>0.02846623835100489</v>
+        <v>0.1103528457155314</v>
       </c>
       <c r="E93" s="11" t="n">
-        <v>0.06430626193373404</v>
+        <v>0.09778359001541834</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>0.06699836548547758</v>
+        <v>0.0692937123890178</v>
       </c>
       <c r="G93" s="11" t="n">
-        <v>0.05584002806837911</v>
+        <v>0.07805244418719343</v>
       </c>
       <c r="H93" s="11" t="n">
-        <v>0.04139724841428747</v>
+        <v>0.08463384936674581</v>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>Location quotient vs U.S.: 1.62x — more concentrated here.</t>
+          <t>Location quotient vs U.S.: 0.82x — less concentrated here.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>Finance/Insurance</t>
         </is>
       </c>
       <c r="B94" s="11" t="n">
-        <v>0.005344531399121969</v>
+        <v>0.01355220461920214</v>
       </c>
       <c r="C94" s="11" t="n">
-        <v>0.03838234842199072</v>
+        <v>0.02564457146369196</v>
       </c>
       <c r="D94" s="11" t="n">
-        <v>0.04546362849167086</v>
+        <v>0.02846623835100489</v>
       </c>
       <c r="E94" s="11" t="n">
-        <v>0.06499302595968018</v>
+        <v>0.06430626193373404</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>0.06180957654864814</v>
+        <v>0.06699836548547758</v>
       </c>
       <c r="G94" s="11" t="n">
-        <v>0.06178450068945185</v>
+        <v>0.05584002806837911</v>
       </c>
       <c r="H94" s="11" t="n">
-        <v>0.08451882031580928</v>
+        <v>0.04139724841428747</v>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>Location quotient vs U.S.: 0.73x — less concentrated here.</t>
+          <t>Location quotient vs U.S.: 1.62x — more concentrated here.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>Professional/Scientific/Tech</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="B95" s="11" t="n">
-        <v>0.03531208245848445</v>
+        <v>0.005344531399121969</v>
       </c>
       <c r="C95" s="11" t="n">
-        <v>0.06550198211487047</v>
+        <v>0.03838234842199072</v>
       </c>
       <c r="D95" s="11" t="n">
-        <v>0.05942728423245309</v>
+        <v>0.04546362849167086</v>
       </c>
       <c r="E95" s="11" t="n">
-        <v>0.06130384568509065</v>
+        <v>0.06499302595968018</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>0.06005544300027939</v>
+        <v>0.06180957654864814</v>
       </c>
       <c r="G95" s="11" t="n">
-        <v>0.05671111569578283</v>
+        <v>0.06178450068945185</v>
       </c>
       <c r="H95" s="11" t="n">
-        <v>0.07101058481218332</v>
+        <v>0.08451882031580928</v>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>Location quotient vs U.S.: 0.85x — less concentrated here.</t>
+          <t>Location quotient vs U.S.: 0.73x — less concentrated here.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>Transportation/Warehousing</t>
+          <t>Professional/Scientific/Tech</t>
         </is>
       </c>
       <c r="B96" s="11" t="n">
-        <v>0.01068906279824394</v>
+        <v>0.03531208245848445</v>
       </c>
       <c r="C96" s="11" t="n">
-        <v>0.006038536000737531</v>
+        <v>0.06550198211487047</v>
       </c>
       <c r="D96" s="11" t="n">
-        <v>0.01906832260525726</v>
+        <v>0.05942728423245309</v>
       </c>
       <c r="E96" s="11" t="n">
-        <v>0.02301916942178338</v>
+        <v>0.06130384568509065</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>0.0473268911935302</v>
+        <v>0.06005544300027939</v>
       </c>
       <c r="G96" s="11" t="n">
-        <v>0.04326179016785311</v>
+        <v>0.05671111569578283</v>
       </c>
       <c r="H96" s="11" t="n">
-        <v>0.04840196213219566</v>
+        <v>0.07101058481218332</v>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>Location quotient vs U.S.: 0.98x — less concentrated here.</t>
+          <t>Location quotient vs U.S.: 0.85x — less concentrated here.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>Wholesale Trade</t>
+          <t>Transportation/Warehousing</t>
         </is>
       </c>
       <c r="B97" s="11" t="n">
-        <v>0.007825920977285742</v>
+        <v>0.01068906279824394</v>
       </c>
       <c r="C97" s="11" t="n">
-        <v>0.03606219845733075</v>
+        <v>0.006038536000737531</v>
       </c>
       <c r="D97" s="11" t="n">
-        <v>0.03811847913626373</v>
+        <v>0.01906832260525726</v>
       </c>
       <c r="E97" s="11" t="n">
-        <v>0.03247329842121656</v>
+        <v>0.02301916942178338</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>0.04109248140049621</v>
+        <v>0.0473268911935302</v>
       </c>
       <c r="G97" s="11" t="n">
-        <v>0.03708044284108286</v>
+        <v>0.04326179016785311</v>
       </c>
       <c r="H97" s="11" t="n">
-        <v>0.03992451539947575</v>
+        <v>0.04840196213219566</v>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>Location quotient vs U.S.: 1.03x — more concentrated here.</t>
+          <t>Location quotient vs U.S.: 0.98x — less concentrated here.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>Public Administration</t>
+          <t>Wholesale Trade</t>
         </is>
       </c>
       <c r="B98" s="11" t="n">
-        <v>0</v>
+        <v>0.007825920977285742</v>
       </c>
       <c r="C98" s="11" t="n">
-        <v>0.001859193018038782</v>
+        <v>0.03606219845733075</v>
       </c>
       <c r="D98" s="11" t="n">
-        <v>0.02761848821930085</v>
+        <v>0.03811847913626373</v>
       </c>
       <c r="E98" s="11" t="n">
-        <v>0.02183329238543132</v>
+        <v>0.03247329842121656</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>0.03285591679200175</v>
+        <v>0.04109248140049621</v>
       </c>
       <c r="G98" s="11" t="n">
-        <v>0.04120792091186574</v>
+        <v>0.03708044284108286</v>
       </c>
       <c r="H98" s="11" t="n">
-        <v>0.04966983338636385</v>
+        <v>0.03992451539947575</v>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>Location quotient vs U.S.: 0.66x — less concentrated here.</t>
+          <t>Location quotient vs U.S.: 1.03x — more concentrated here.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>Other Services</t>
+          <t>Public Administration</t>
         </is>
       </c>
       <c r="B99" s="11" t="n">
-        <v>0.01546096583317427</v>
+        <v>0</v>
       </c>
       <c r="C99" s="11" t="n">
-        <v>0.02945514888909376</v>
+        <v>0.001859193018038782</v>
       </c>
       <c r="D99" s="11" t="n">
-        <v>0.03031917792458657</v>
+        <v>0.02761848821930085</v>
       </c>
       <c r="E99" s="11" t="n">
-        <v>0.02663677147395037</v>
+        <v>0.02183329238543132</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>0.02745633069056147</v>
+        <v>0.03285591679200175</v>
       </c>
       <c r="G99" s="11" t="n">
-        <v>0.02813810432102126</v>
+        <v>0.04120792091186574</v>
       </c>
       <c r="H99" s="11" t="n">
-        <v>0.03015265325357227</v>
+        <v>0.04966983338636385</v>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>Location quotient vs U.S.: 0.91x — less concentrated here.</t>
+          <t>Location quotient vs U.S.: 0.66x — less concentrated here.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>Arts/Entertainment/Rec</t>
+          <t>Other Services</t>
         </is>
       </c>
       <c r="B100" s="11" t="n">
-        <v>0.2744798625691926</v>
+        <v>0.01546096583317427</v>
       </c>
       <c r="C100" s="11" t="n">
-        <v>0.03211333394794259</v>
+        <v>0.02945514888909376</v>
       </c>
       <c r="D100" s="11" t="n">
-        <v>0.0287326741066833</v>
+        <v>0.03031917792458657</v>
       </c>
       <c r="E100" s="11" t="n">
-        <v>0.02107301559051066</v>
+        <v>0.02663677147395037</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>0.02090656164729619</v>
+        <v>0.02745633069056147</v>
       </c>
       <c r="G100" s="11" t="n">
-        <v>0.02117990984115704</v>
+        <v>0.02813810432102126</v>
       </c>
       <c r="H100" s="11" t="n">
-        <v>0.01844252444674844</v>
+        <v>0.03015265325357227</v>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>Location quotient vs U.S.: 1.13x — more concentrated here.</t>
+          <t>Location quotient vs U.S.: 0.91x — less concentrated here.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>Real Estate/Rental</t>
+          <t>Arts/Entertainment/Rec</t>
         </is>
       </c>
       <c r="B101" s="11" t="n">
-        <v>0.03340332124451231</v>
+        <v>0.2744798625691926</v>
       </c>
       <c r="C101" s="11" t="n">
-        <v>0.03411081404996773</v>
+        <v>0.03211333394794259</v>
       </c>
       <c r="D101" s="11" t="n">
-        <v>0.02407610374039469</v>
+        <v>0.0287326741066833</v>
       </c>
       <c r="E101" s="11" t="n">
-        <v>0.02037464428525276</v>
+        <v>0.02107301559051066</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>0.02084382439592392</v>
+        <v>0.02090656164729619</v>
       </c>
       <c r="G101" s="11" t="n">
-        <v>0.01961125167587262</v>
+        <v>0.02117990984115704</v>
       </c>
       <c r="H101" s="11" t="n">
-        <v>0.01586685774361</v>
+        <v>0.01844252444674844</v>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>Location quotient vs U.S.: 1.31x — more concentrated here.</t>
+          <t>Location quotient vs U.S.: 1.13x — more concentrated here.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>Real Estate/Rental</t>
         </is>
       </c>
       <c r="B102" s="11" t="n">
-        <v>0.002672265699560985</v>
+        <v>0.03340332124451231</v>
       </c>
       <c r="C102" s="11" t="n">
-        <v>0.01090931440336806</v>
+        <v>0.03411081404996773</v>
       </c>
       <c r="D102" s="11" t="n">
-        <v>0.01293424486657018</v>
+        <v>0.02407610374039469</v>
       </c>
       <c r="E102" s="11" t="n">
-        <v>0.01705883149519169</v>
+        <v>0.02037464428525276</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>0.01906250470529385</v>
+        <v>0.02084382439592392</v>
       </c>
       <c r="G102" s="11" t="n">
-        <v>0.01736157873170788</v>
+        <v>0.01961125167587262</v>
       </c>
       <c r="H102" s="11" t="n">
-        <v>0.02037764401856688</v>
+        <v>0.01586685774361</v>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>Location quotient vs U.S.: 0.94x — less concentrated here.</t>
+          <t>Location quotient vs U.S.: 1.31x — more concentrated here.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>Mgmt of Companies</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="B103" s="11" t="n">
-        <v>0.0005726283641916397</v>
+        <v>0.002672265699560985</v>
       </c>
       <c r="C103" s="11" t="n">
-        <v>0.01676346762545712</v>
+        <v>0.01090931440336806</v>
       </c>
       <c r="D103" s="11" t="n">
-        <v>0.01896538151783606</v>
+        <v>0.01293424486657018</v>
       </c>
       <c r="E103" s="11" t="n">
-        <v>0.01917522542303697</v>
+        <v>0.01705883149519169</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>0.01809509628913341</v>
+        <v>0.01906250470529385</v>
       </c>
       <c r="G103" s="11" t="n">
-        <v>0.01520137056214125</v>
+        <v>0.01736157873170788</v>
       </c>
       <c r="H103" s="11" t="n">
-        <v>0.0166872404072684</v>
+        <v>0.02037764401856688</v>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>Location quotient vs U.S.: 1.08x — more concentrated here.</t>
+          <t>Location quotient vs U.S.: 0.94x — less concentrated here.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Mgmt of Companies</t>
         </is>
       </c>
       <c r="B104" s="11" t="n">
-        <v>0.001145256728383279</v>
+        <v>0.0005726283641916397</v>
       </c>
       <c r="C104" s="11" t="n">
-        <v>0.0007221658830398574</v>
+        <v>0.01676346762545712</v>
       </c>
       <c r="D104" s="11" t="n">
-        <v>0.003772488086082971</v>
+        <v>0.01896538151783606</v>
       </c>
       <c r="E104" s="11" t="n">
-        <v>0.002512975970997278</v>
+        <v>0.01917522542303697</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>0.006769767671410718</v>
+        <v>0.01809509628913341</v>
       </c>
       <c r="G104" s="11" t="n">
-        <v>0.006825111647899759</v>
+        <v>0.01520137056214125</v>
       </c>
       <c r="H104" s="11" t="n">
-        <v>0.0054838649167028</v>
+        <v>0.0166872404072684</v>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>Location quotient vs U.S.: 1.23x — more concentrated here.</t>
+          <t>Location quotient vs U.S.: 1.08x — more concentrated here.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>Agriculture/Forestry/Fishing</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="B105" s="11" t="n">
-        <v>0</v>
+        <v>0.001145256728383279</v>
       </c>
       <c r="C105" s="11" t="n">
-        <v>0.0006299744937156203</v>
+        <v>0.0007221658830398574</v>
       </c>
       <c r="D105" s="11" t="n">
-        <v>0.001725777053826078</v>
+        <v>0.003772488086082971</v>
       </c>
       <c r="E105" s="11" t="n">
-        <v>0.001151055198416767</v>
+        <v>0.002512975970997278</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>0.003239751660864168</v>
+        <v>0.006769767671410718</v>
       </c>
       <c r="G105" s="11" t="n">
-        <v>0.007704795534784445</v>
+        <v>0.006825111647899759</v>
       </c>
       <c r="H105" s="11" t="n">
-        <v>0.008224135502638645</v>
+        <v>0.0054838649167028</v>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>Location quotient vs U.S.: 0.39x — less concentrated here.</t>
+          <t>Location quotient vs U.S.: 1.23x — more concentrated here.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>Mining/Oil &amp; Gas</t>
+          <t>Agriculture/Forestry/Fishing</t>
         </is>
       </c>
       <c r="B106" s="11" t="n">
         <v>0</v>
       </c>
       <c r="C106" s="11" t="n">
+        <v>0.0006299744937156203</v>
+      </c>
+      <c r="D106" s="11" t="n">
+        <v>0.001725777053826078</v>
+      </c>
+      <c r="E106" s="11" t="n">
+        <v>0.001151055198416767</v>
+      </c>
+      <c r="F106" s="11" t="n">
+        <v>0.003239751660864168</v>
+      </c>
+      <c r="G106" s="11" t="n">
+        <v>0.007704795534784445</v>
+      </c>
+      <c r="H106" s="11" t="n">
+        <v>0.008224135502638645</v>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>Location quotient vs U.S.: 0.39x — less concentrated here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>Mining/Oil &amp; Gas</t>
+        </is>
+      </c>
+      <c r="B107" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C107" s="11" t="n">
         <v>0.0006760701883777388</v>
       </c>
-      <c r="D106" s="11" t="n">
+      <c r="D107" s="11" t="n">
         <v>0.0003814875592668172</v>
       </c>
-      <c r="E106" s="11" t="n">
+      <c r="E107" s="11" t="n">
         <v>0.0003985165897039564</v>
       </c>
-      <c r="F106" s="11" t="n">
+      <c r="F107" s="11" t="n">
         <v>0.00144881225835702</v>
       </c>
-      <c r="G106" s="11" t="n">
+      <c r="G107" s="11" t="n">
         <v>0.004149446289456433</v>
       </c>
-      <c r="H106" s="11" t="n">
+      <c r="H107" s="11" t="n">
         <v>0.003822849608574414</v>
       </c>
-      <c r="I106" s="2" t="inlineStr">
+      <c r="I107" s="2" t="inlineStr">
         <is>
           <t>Location quotient vs U.S.: 0.38x — less concentrated here.</t>
         </is>
@@ -8776,7 +8783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -8826,7 +8833,7 @@
         </is>
       </c>
       <c r="B5" s="23" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6">
@@ -8984,22 +8991,22 @@
     <row r="12">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>comps.rows</t>
+          <t>comps.nearby[].units</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>19 entries</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape, via the market-report service</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>POST /report (format json)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -9010,94 +9017,94 @@
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="22" t="inlineStr">
         <is>
-          <t>Own weekly scrape; asking and net effective stated separately.</t>
+          <t>Unit counts come from a licensed data export; the internal pipeline carries them.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>comps.rows.tier</t>
+          <t>comps.rows</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19 entries</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Tracked-community registry, via the market-report service</t>
+          <t>Operator's own weekly rent scrape, via the market-report service</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>comp_tiers.assign</t>
+          <t>POST /report (format json)</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>comps.rows.distance_mi, comps.tiering.subject_product, comps.tiering.subject_year_built, comps.tiering.year_band, comps.tiering.top_n, comps.tiering.additional_n</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="n"/>
       <c r="G13" s="22" t="inlineStr">
         <is>
-          <t>Closest same-product communities first, within the vintage band where the registry carries a year built; an unknown year keeps the community and says so.</t>
+          <t>Own weekly scrape; asking and net effective stated separately.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>demand.rings</t>
+          <t>comps.rows.tier</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>5 entries</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Public demographic data (the operator's ring engine), via the market-report service</t>
+          <t>Tracked-community registry, via the market-report service</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>POST /report (format json)</t>
+          <t>comp_tiers.assign</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F14" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>comps.rows.distance_mi, comps.tiering.subject_product, comps.tiering.subject_year_built, comps.tiering.year_band, comps.tiering.top_n, comps.tiering.additional_n</t>
+        </is>
+      </c>
       <c r="G14" s="22" t="inlineStr">
         <is>
-          <t>Ring demographics.</t>
+          <t>Closest same-product communities first, within the vintage band where the registry carries a year built; an unknown year keeps the community and says so.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>demand.zip_home</t>
+          <t>demand.rings</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5 entries</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Zillow ZHVI home values (vendored static table, undated), via the market-report service</t>
+          <t>Public demographic data (the operator's ring engine), via the market-report service</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -9113,29 +9120,29 @@
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="22" t="inlineStr">
         <is>
-          <t>ZIP and metro home values from the vendored Zillow ZHVI table; static, undated.</t>
+          <t>Ring demographics.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>om_comps.rent</t>
+          <t>demand.zip_home</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>0 entries</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
+          <t>Zillow ZHVI home values (vendored static table, undated), via the market-report service</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>p.20</t>
+          <t>POST /report (format json)</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -9146,29 +9153,29 @@
       <c r="F16" s="12" t="n"/>
       <c r="G16" s="22" t="inlineStr">
         <is>
-          <t>4 rent comparable(s) the memorandum states; every figure verified inside its own quote.</t>
+          <t>ZIP and metro home values from the vendored Zillow ZHVI table; static, undated.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>pricing.price_per_unit</t>
+          <t>om_comps.rent</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>215,000</t>
+          <t>0 entries</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Illustrative price</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>p.20</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -9179,24 +9186,24 @@
       <c r="F17" s="12" t="n"/>
       <c r="G17" s="22" t="inlineStr">
         <is>
-          <t>Per-unit price chosen for the sample, inside the sale-price band; every cap rate and pricing ladder is computed from it.</t>
+          <t>4 rent comparable(s) the memorandum states; every figure verified inside its own quote.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>pricing.unit_count</t>
+          <t>pricing.price_per_unit</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>215,000</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Sample Property RR 8.4.26.xlsx</t>
+          <t>Illustrative price</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -9206,34 +9213,30 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>summary.unit_count</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="n"/>
       <c r="G18" s="22" t="inlineStr">
         <is>
-          <t>The same count the summary carries, counted from the rows of the uploaded rent roll.</t>
+          <t>Per-unit price chosen for the sample, inside the sale-price band; every cap rate and pricing ladder is computed from it.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="24" t="inlineStr">
         <is>
-          <t>summary.address_provenance</t>
+          <t>pricing.unit_count</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for t…</t>
+          <t>334</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Illustrative address</t>
+          <t>Sample Property RR 8.4.26.xlsx</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -9243,30 +9246,34 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F19" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>summary.unit_count</t>
+        </is>
+      </c>
       <c r="G19" s="22" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
+          <t>The same count the summary carries, counted from the rows of the uploaded rent roll.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>summary.assessed_value_basis</t>
+          <t>summary.address_provenance</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for t…</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Illustrative address</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -9282,29 +9289,29 @@
       <c r="F20" s="12" t="n"/>
       <c r="G20" s="22" t="inlineStr">
         <is>
-          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>summary.assessment_ratio</t>
+          <t>summary.assessed_value_basis</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Vendored county rate table</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>property_tax_table.STATE_RULES['AZ']</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -9315,29 +9322,29 @@
       <c r="F21" s="12" t="n"/>
       <c r="G21" s="22" t="inlineStr">
         <is>
-          <t>10% — legal class 4.2, residential rental. A.R.S. sec. 42-15003 (class four assessed at 10%); A.R.S. sec. 42-12004 (class four includes residential rental property).</t>
+          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="24" t="inlineStr">
         <is>
-          <t>summary.city</t>
+          <t>summary.assessment_ratio</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Mesa</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Illustrative address</t>
+          <t>Vendored county rate table</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>property_tax_table.STATE_RULES['AZ']</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -9348,24 +9355,24 @@
       <c r="F22" s="12" t="n"/>
       <c r="G22" s="22" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
+          <t>10% — legal class 4.2, residential rental. A.R.S. sec. 42-15003 (class four assessed at 10%); A.R.S. sec. 42-12004 (class four includes residential rental property).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="24" t="inlineStr">
         <is>
-          <t>summary.construction_status</t>
+          <t>summary.city</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>Mesa</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Not stated in the uploaded documents</t>
+          <t>Illustrative address</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -9381,24 +9388,24 @@
       <c r="F23" s="12" t="n"/>
       <c r="G23" s="22" t="inlineStr">
         <is>
-          <t>No uploaded document stated this, so the value reads MISSING. Nothing was assumed to fill it.</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="24" t="inlineStr">
         <is>
-          <t>summary.county</t>
+          <t>summary.construction_status</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Maricopa</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Illustrative address</t>
+          <t>Not stated in the uploaded documents</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -9414,24 +9421,24 @@
       <c r="F24" s="12" t="n"/>
       <c r="G24" s="22" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
+          <t>No uploaded document stated this, so the value reads MISSING. Nothing was assumed to fill it.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="24" t="inlineStr">
         <is>
-          <t>summary.deal_name</t>
+          <t>summary.county</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Sample Mesa Apt</t>
+          <t>Maricopa</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Illustrative name</t>
+          <t>Illustrative address</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -9447,24 +9454,24 @@
       <c r="F25" s="12" t="n"/>
       <c r="G25" s="22" t="inlineStr">
         <is>
-          <t>An illustrative name for the public sample. The real asset's name is withheld; the memorandum's own name for it does not appear anywhere in this set.</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
         <is>
-          <t>summary.deal_status</t>
+          <t>summary.deal_name</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>Sample Mesa Apt</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Not stated in the uploaded documents</t>
+          <t>Illustrative name</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -9480,14 +9487,14 @@
       <c r="F26" s="12" t="n"/>
       <c r="G26" s="22" t="inlineStr">
         <is>
-          <t>No uploaded document stated this, so the value reads MISSING. Nothing was assumed to fill it.</t>
+          <t>An illustrative name for the public sample. The real asset's name is withheld; the memorandum's own name for it does not appear anywhere in this set.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="24" t="inlineStr">
         <is>
-          <t>summary.delivery_date</t>
+          <t>summary.deal_status</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -9520,7 +9527,7 @@
     <row r="28">
       <c r="A28" s="24" t="inlineStr">
         <is>
-          <t>summary.fair_market_value</t>
+          <t>summary.delivery_date</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -9530,7 +9537,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Not stated in the uploaded documents</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -9546,24 +9553,24 @@
       <c r="F28" s="12" t="n"/>
       <c r="G28" s="22" t="inlineStr">
         <is>
-          <t>The internal pipeline pulls a market value by web lookup; the demo does not reach the web.</t>
+          <t>No uploaded document stated this, so the value reads MISSING. Nothing was assumed to fill it.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="24" t="inlineStr">
         <is>
-          <t>summary.in_place_rent_avg</t>
+          <t>summary.fair_market_value</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>1,456.99</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Sample Property RR 8.4.26.xlsx</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -9573,34 +9580,30 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>rent_roll.units</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="n"/>
       <c r="G29" s="22" t="inlineStr">
         <is>
-          <t>Unit-weighted across the uploaded roll.</t>
+          <t>The internal pipeline pulls a market value by web lookup; the demo does not reach the web.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="24" t="inlineStr">
         <is>
-          <t>summary.listing_brokerage</t>
+          <t>summary.in_place_rent_avg</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Desert Ridge Capital Advisors</t>
+          <t>1,456.99</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Illustrative name</t>
+          <t>Sample Property RR 8.4.26.xlsx</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -9610,30 +9613,34 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F30" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>rent_roll.units</t>
+        </is>
+      </c>
       <c r="G30" s="22" t="inlineStr">
         <is>
-          <t>An illustrative name. The real party is withheld from the public sample.</t>
+          <t>Unit-weighted across the uploaded roll.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="24" t="inlineStr">
         <is>
-          <t>summary.market_rent_for_model</t>
+          <t>summary.listing_brokerage</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>1,344.6</t>
+          <t>Desert Ridge Capital Advisors</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Sample Property RR 8.4.26.xlsx</t>
+          <t>Illustrative name</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -9643,34 +9650,30 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>rent_roll.units</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="n"/>
       <c r="G31" s="22" t="inlineStr">
         <is>
-          <t>Unit-weighted across the uploaded roll.</t>
+          <t>An illustrative name. The real party is withheld from the public sample.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="24" t="inlineStr">
         <is>
-          <t>summary.msa</t>
+          <t>summary.market_rent_for_model</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Phoenix MSA</t>
+          <t>1,344.6</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Illustrative address</t>
+          <t>Sample Property RR 8.4.26.xlsx</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -9680,30 +9683,34 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F32" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>rent_roll.units</t>
+        </is>
+      </c>
       <c r="G32" s="22" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
+          <t>Unit-weighted across the uploaded roll.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="24" t="inlineStr">
         <is>
-          <t>summary.pricing_guidance</t>
+          <t>summary.msa</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>$215,000 per unit (illustrative)</t>
+          <t>Phoenix MSA</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Illustrative price</t>
+          <t>Illustrative address</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -9719,29 +9726,29 @@
       <c r="F33" s="12" t="n"/>
       <c r="G33" s="22" t="inlineStr">
         <is>
-          <t>Every price and cap rate below is illustrative. The per-unit price is a round number chosen for the sample inside the band a real per-unit sale price occupies; it is not a quote, an offer, or a broker's guidance.</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="24" t="inlineStr">
         <is>
-          <t>summary.product_detail</t>
+          <t>summary.pricing_guidance</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Diversified mix of one-, two-, and three-bedroom residences averaging 856 square feet o…</t>
+          <t>$215,000 per unit (illustrative)</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
+          <t>Illustrative price</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>p.3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -9751,6 +9758,39 @@
       </c>
       <c r="F34" s="12" t="n"/>
       <c r="G34" s="22" t="inlineStr">
+        <is>
+          <t>Every price and cap rate below is illustrative. The per-unit price is a round number chosen for the sample inside the band a real per-unit sale price occupies; it is not a quote, an offer, or a broker's guidance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>summary.product_detail</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Diversified mix of one-, two-, and three-bedroom residences averaging 856 square feet o…</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Sample Property Offering Memorandum.pdf</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>p.3</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="n"/>
+      <c r="G35" s="22" t="inlineStr">
         <is>
           <t>the property offers a diversified mix of 
 one-, two-, and three-bedroom residences averaging 856 square 
@@ -9758,58 +9798,25 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="24" t="inlineStr">
-        <is>
-          <t>summary.product_type</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>Garden-style multifamily</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>p.3</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F35" s="12" t="n"/>
-      <c r="G35" s="22" t="inlineStr">
-        <is>
-          <t>Stated in the memorandum; withheld from the public sample because it identifies the real asset.</t>
-        </is>
-      </c>
-    </row>
     <row r="36">
       <c r="A36" s="24" t="inlineStr">
         <is>
-          <t>summary.school_elementary_name</t>
+          <t>summary.product_type</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Porter Elementary School</t>
+          <t>Garden-style multifamily</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Internal underwriting agent — attendance-zone school lookup</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>2151 E Southern Ave, Mesa, AZ 85204 on 2026-09-14</t>
+          <t>p.3</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -9820,19 +9827,19 @@
       <c r="F36" s="12" t="n"/>
       <c r="G36" s="22" t="inlineStr">
         <is>
-          <t>Looked up for the illustrative address by the internal underwriting agent; the public demo does not run this on an uploaded deal.</t>
+          <t>Stated in the memorandum; withheld from the public sample because it identifies the real asset.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="24" t="inlineStr">
         <is>
-          <t>summary.school_high_name</t>
+          <t>summary.school_elementary_name</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Mesa High School</t>
+          <t>Porter Elementary School</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -9860,12 +9867,12 @@
     <row r="38">
       <c r="A38" s="24" t="inlineStr">
         <is>
-          <t>summary.school_middle_name</t>
+          <t>summary.school_high_name</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Taylor Junior High School</t>
+          <t>Mesa High School</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -9893,22 +9900,22 @@
     <row r="39">
       <c r="A39" s="24" t="inlineStr">
         <is>
-          <t>summary.seller_entity</t>
+          <t>summary.school_middle_name</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Sonoran Residential Holdings LLC</t>
+          <t>Taylor Junior High School</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Illustrative name</t>
+          <t>Internal underwriting agent — attendance-zone school lookup</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2151 E Southern Ave, Mesa, AZ 85204 on 2026-09-14</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -9919,24 +9926,24 @@
       <c r="F39" s="12" t="n"/>
       <c r="G39" s="22" t="inlineStr">
         <is>
-          <t>An illustrative name. The real party is withheld from the public sample.</t>
+          <t>Looked up for the illustrative address by the internal underwriting agent; the public demo does not run this on an uploaded deal.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="24" t="inlineStr">
         <is>
-          <t>summary.state</t>
+          <t>summary.seller_entity</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Sonoran Residential Holdings LLC</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Illustrative address</t>
+          <t>Illustrative name</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -9952,19 +9959,19 @@
       <c r="F40" s="12" t="n"/>
       <c r="G40" s="22" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
+          <t>An illustrative name. The real party is withheld from the public sample.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="24" t="inlineStr">
         <is>
-          <t>summary.street_address</t>
+          <t>summary.state</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>2151 E Southern Ave</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -9992,22 +9999,22 @@
     <row r="42">
       <c r="A42" s="24" t="inlineStr">
         <is>
-          <t>summary.structure</t>
+          <t>summary.street_address</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>1 &amp; 2 stories</t>
+          <t>2151 E Southern Ave</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
+          <t>Illustrative address</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>p.10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -10018,29 +10025,29 @@
       <c r="F42" s="12" t="n"/>
       <c r="G42" s="22" t="inlineStr">
         <is>
-          <t>Number of Stories 1 &amp; 2</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="24" t="inlineStr">
         <is>
-          <t>summary.tax_area_code</t>
+          <t>summary.structure</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>1 &amp; 2 stories</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>p.10</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -10051,29 +10058,29 @@
       <c r="F43" s="12" t="n"/>
       <c r="G43" s="22" t="inlineStr">
         <is>
-          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
+          <t>Number of Stories 1 &amp; 2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="24" t="inlineStr">
         <is>
-          <t>summary.tax_basis_label</t>
+          <t>summary.tax_area_code</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Limited property value (LPV), per the county assessor</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Vendored county rate table</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>property_tax_table.STATE_RULES['AZ']</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -10084,19 +10091,19 @@
       <c r="F44" s="12" t="n"/>
       <c r="G44" s="22" t="inlineStr">
         <is>
-          <t>What the assessed basis is in this state.</t>
+          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="24" t="inlineStr">
         <is>
-          <t>summary.tax_basis_note</t>
+          <t>summary.tax_basis_label</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Arizona taxes the limited property value, not the price. Under Proposition 117 (Ariz. C…</t>
+          <t>Limited property value (LPV), per the county assessor</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -10117,29 +10124,29 @@
       <c r="F45" s="12" t="n"/>
       <c r="G45" s="22" t="inlineStr">
         <is>
-          <t>How the basis behaves on a sale, with the authority.</t>
+          <t>What the assessed basis is in this state.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="24" t="inlineStr">
         <is>
-          <t>summary.tax_billed_amount</t>
+          <t>summary.tax_basis_note</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>249,122</t>
+          <t>Arizona taxes the limited property value, not the price. Under Proposition 117 (Ariz. C…</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
+          <t>Vendored county rate table</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>p.10</t>
+          <t>property_tax_table.STATE_RULES['AZ']</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -10150,19 +10157,19 @@
       <c r="F46" s="12" t="n"/>
       <c r="G46" s="22" t="inlineStr">
         <is>
-          <t>2025 Property Tax $249,122</t>
+          <t>How the basis behaves on a sale, with the authority.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="24" t="inlineStr">
         <is>
-          <t>summary.tax_billed_year</t>
+          <t>summary.tax_billed_amount</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>2,025</t>
+          <t>249,122</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -10190,22 +10197,22 @@
     <row r="48">
       <c r="A48" s="24" t="inlineStr">
         <is>
-          <t>summary.tax_divisor</t>
+          <t>summary.tax_billed_year</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>2,025</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Vendored county rate table</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>property_tax_table.STATE_RULES['AZ']</t>
+          <t>p.10</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -10216,29 +10223,29 @@
       <c r="F48" s="12" t="n"/>
       <c r="G48" s="22" t="inlineStr">
         <is>
-          <t>The rate's unit in Arizona: per $100 of assessed value.</t>
+          <t>2025 Property Tax $249,122</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="24" t="inlineStr">
         <is>
-          <t>summary.tax_exemption</t>
+          <t>summary.tax_divisor</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Vendored county rate table</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>property_tax_table.STATE_RULES['AZ']</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -10249,29 +10256,29 @@
       <c r="F49" s="12" t="n"/>
       <c r="G49" s="22" t="inlineStr">
         <is>
-          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
+          <t>The rate's unit in Arizona: per $100 of assessed value.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="24" t="inlineStr">
         <is>
-          <t>summary.tax_parcel_id</t>
+          <t>summary.tax_exemption</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>301-04-002K</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>p.10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -10282,56 +10289,52 @@
       <c r="F50" s="12" t="n"/>
       <c r="G50" s="22" t="inlineStr">
         <is>
-          <t>Tax Parcel Number 301-04-002K</t>
+          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="24" t="inlineStr">
         <is>
-          <t>summary.tax_per_unit_flag</t>
+          <t>summary.tax_parcel_id</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>In band (the statement's line per unit): $717 per unit a year is inside the AZ band of …</t>
+          <t>301-04-002K</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Vendored county rate table</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>property_tax_table.band_check</t>
+          <t>p.10</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>summary.tax_statement_amount, summary.unit_count, summary.state</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="n"/>
       <c r="G51" s="22" t="inlineStr">
         <is>
-          <t>A sanity check against the state's typical per-unit range. It flags; it never changes a figure.</t>
+          <t>Tax Parcel Number 301-04-002K</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="24" t="inlineStr">
         <is>
-          <t>summary.tax_rate_as_billed</t>
+          <t>summary.tax_per_unit_flag</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>10.26</t>
+          <t>In band (the statement's line per unit): $717 per unit a year is inside the AZ band of …</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -10341,30 +10344,34 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>property_tax_table.COUNTY_RATES[('AZ', 'maricopa')]</t>
+          <t>property_tax_table.band_check</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F52" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>summary.tax_statement_amount, summary.unit_count, summary.state</t>
+        </is>
+      </c>
       <c r="G52" s="22" t="inlineStr">
         <is>
-          <t>Tax area code 971300 — City of Phoenix / Deer Valley Unified School District #97, tax year 2025. Maricopa County, '2025 Tax Rates, Maricopa County, Arizona' (the treasurer's rate table by tax area code), row 971300: primary 6.7007, approx residential primary 5.1401, secondary 3.5566. Verified 2026-09-04.</t>
+          <t>A sanity check against the state's typical per-unit range. It flags; it never changes a figure.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="24" t="inlineStr">
         <is>
-          <t>summary.tax_rate_evidence</t>
+          <t>summary.tax_rate_as_billed</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Vendored county rate table: 10.2573 per $100 of assessed value, tax year 2025 — Tax are…</t>
+          <t>10.26</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -10374,34 +10381,30 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>property_tax_table.evidence_text</t>
+          <t>property_tax_table.COUNTY_RATES[('AZ', 'maricopa')]</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>summary.state, summary.county, summary.tax_parcel_id, summary.tax_billed_amount, summary.tax_billed_year</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F53" s="12" t="n"/>
       <c r="G53" s="22" t="inlineStr">
         <is>
-          <t>The citation, tax year and jurisdiction stack behind the rate, or the honest note that none is on file. Also records what the uploaded document stated for the field(s) it cites.</t>
+          <t>Tax area code 971300 — City of Phoenix / Deer Valley Unified School District #97, tax year 2025. Maricopa County, '2025 Tax Rates, Maricopa County, Arizona' (the treasurer's rate table by tax area code), row 971300: primary 6.7007, approx residential primary 5.1401, secondary 3.5566. Verified 2026-09-04.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="24" t="inlineStr">
         <is>
-          <t>summary.tax_rate_year</t>
+          <t>summary.tax_rate_evidence</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>2,025</t>
+          <t>Vendored county rate table: 10.2573 per $100 of assessed value, tax year 2025 — Tax are…</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
@@ -10411,147 +10414,151 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>property_tax_table.COUNTY_RATES[('AZ', 'maricopa')]</t>
+          <t>property_tax_table.evidence_text</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F54" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>summary.state, summary.county, summary.tax_parcel_id, summary.tax_billed_amount, summary.tax_billed_year</t>
+        </is>
+      </c>
       <c r="G54" s="22" t="inlineStr">
         <is>
-          <t>The tax year of the rate on file. A bill from another year is displayed, not tied out.</t>
+          <t>The citation, tax year and jurisdiction stack behind the rate, or the honest note that none is on file. Also records what the uploaded document stated for the field(s) it cites.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="24" t="inlineStr">
         <is>
-          <t>summary.tax_statement_amount</t>
+          <t>summary.tax_rate_year</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>239,566.79</t>
+          <t>2,025</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Sample Property T-12 June 26.xlsx</t>
+          <t>Vendored county rate table</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Property Taxes lines</t>
+          <t>property_tax_table.COUNTY_RATES[('AZ', 'maricopa')]</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>computed</t>
-        </is>
-      </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>t12.rows</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="n"/>
       <c r="G55" s="22" t="inlineStr">
         <is>
-          <t>The statement's lines categorised as Property Taxes, summed over its twelve months. As billed in the statement, not the county's bill.</t>
+          <t>The tax year of the rate on file. A bill from another year is displayed, not tied out.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="24" t="inlineStr">
         <is>
-          <t>summary.unit_count</t>
+          <t>summary.tax_statement_amount</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>239,566.79</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Sample Property RR 8.4.26.xlsx</t>
+          <t>Sample Property T-12 June 26.xlsx</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Property Taxes lines</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>computed</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>rent_roll.units</t>
+          <t>t12.rows</t>
         </is>
       </c>
       <c r="G56" s="22" t="inlineStr">
         <is>
-          <t>Counted from the rows of the uploaded rent roll.</t>
+          <t>The statement's lines categorised as Property Taxes, summed over its twelve months. As billed in the statement, not the county's bill.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="24" t="inlineStr">
         <is>
-          <t>summary.year_built</t>
+          <t>summary.unit_count</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>1,981</t>
+          <t>334</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
+          <t>Sample Property RR 8.4.26.xlsx</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>p.10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F57" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>rent_roll.units</t>
+        </is>
+      </c>
       <c r="G57" s="22" t="inlineStr">
         <is>
-          <t>Y ear Built 1981</t>
+          <t>Counted from the rows of the uploaded rent roll.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="24" t="inlineStr">
         <is>
-          <t>summary.zip</t>
+          <t>summary.year_built</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>85204</t>
+          <t>1,981</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Illustrative address</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>p.10</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -10562,75 +10569,108 @@
       <c r="F58" s="12" t="n"/>
       <c r="G58" s="22" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
+          <t>Y ear Built 1981</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="24" t="inlineStr">
         <is>
-          <t>supply.projects</t>
+          <t>summary.zip</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>32 entries</t>
+          <t>85204</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Public permit and entitlement records (the operator's supply pipeline), via the market-report service</t>
+          <t>Illustrative address</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>POST /report (format json)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>supply.rings</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F59" s="12" t="n"/>
       <c r="G59" s="22" t="inlineStr">
         <is>
-          <t>The developments the counts are made of, within 3 mi: one row per development, reconciled across the pipeline's lifecycle layers and shown at the furthest stage any layer carries.</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="24" t="inlineStr">
         <is>
+          <t>supply.projects</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>32 entries</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>Public permit and entitlement records (the operator's supply pipeline), via the market-report service</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>POST /report (format json)</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
           <t>supply.rings</t>
         </is>
       </c>
-      <c r="B60" s="5" t="inlineStr">
+      <c r="G60" s="22" t="inlineStr">
+        <is>
+          <t>The developments the counts are made of, within 3 mi: one row per development, reconciled across the pipeline's lifecycle layers and shown at the furthest stage any layer carries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="24" t="inlineStr">
+        <is>
+          <t>supply.rings</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
         <is>
           <t>8 entries</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
+      <c r="C61" s="5" t="inlineStr">
         <is>
           <t>Public permit and entitlement records (the operator's supply pipeline), via the market-report service</t>
         </is>
       </c>
-      <c r="D60" s="5" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>POST /report (format json)</t>
         </is>
       </c>
-      <c r="E60" s="5" t="inlineStr">
+      <c r="E61" s="5" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="F60" s="12" t="n"/>
-      <c r="G60" s="22" t="inlineStr">
+      <c r="F61" s="12" t="n"/>
+      <c r="G61" s="22" t="inlineStr">
         <is>
           <t>Projects and units by cumulative ring and tracked stage, counted from the service's project rows.</t>
         </is>

--- a/public/downloads/underwriting-demo/sample-deal-summary.xlsx
+++ b/public/downloads/underwriting-demo/sample-deal-summary.xlsx
@@ -694,7 +694,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-10-06.</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1527,7 +1527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N58"/>
+  <dimension ref="A1:N81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1535,7 +1535,7 @@
     <col width="42" customWidth="1" min="3" max="3"/>
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
@@ -1556,7 +1556,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Mesa Apt — as of 2026-09-03</t>
+          <t>Sample Mesa Apt — as of 2026-09-30</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>1BR — group floor (lowest listing); the lowest-five measure was not provided</t>
+          <t>1BR — lowest five of 5 available</t>
         </is>
       </c>
       <c r="E8" s="15" t="n">
@@ -1693,13 +1693,13 @@
         <v>688</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>1047</v>
+        <v>1199.8</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>1047</v>
+        <v>1199.8</v>
       </c>
       <c r="K8" s="16">
         <f>IFERROR(H8/G8,"")</f>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="L8" s="12" t="n"/>
       <c r="M8" s="17" t="n">
-        <v>46268</v>
+        <v>46295</v>
       </c>
       <c r="N8" s="5" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>1BR — group floor (lowest listing); the lowest-five measure was not provided</t>
+          <t>1BR — lowest five of 9 available</t>
         </is>
       </c>
       <c r="E9" s="15" t="n">
@@ -1740,13 +1740,13 @@
         <v>625</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>978</v>
+        <v>996</v>
       </c>
       <c r="I9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>978</v>
+        <v>996</v>
       </c>
       <c r="K9" s="16">
         <f>IFERROR(H9/G9,"")</f>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="L9" s="12" t="n"/>
       <c r="M9" s="17" t="n">
-        <v>46267</v>
+        <v>46294</v>
       </c>
       <c r="N9" s="5" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>2BR — group floor (lowest listing); the lowest-five measure was not provided</t>
+          <t>2BR — lowest five of 9 available</t>
         </is>
       </c>
       <c r="E10" s="15" t="n">
@@ -1787,13 +1787,13 @@
         <v>725</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>1306</v>
+        <v>1186</v>
       </c>
       <c r="I10" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>1306</v>
+        <v>1186</v>
       </c>
       <c r="K10" s="16">
         <f>IFERROR(H10/G10,"")</f>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="L10" s="12" t="n"/>
       <c r="M10" s="17" t="n">
-        <v>46267</v>
+        <v>46294</v>
       </c>
       <c r="N10" s="5" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>1BR — group floor (lowest listing); the lowest-five measure was not provided</t>
+          <t>1BR — lowest five of 6 available</t>
         </is>
       </c>
       <c r="E11" s="15" t="n">
@@ -1834,13 +1834,13 @@
         <v>579</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>1201</v>
+        <v>1243</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>139</v>
+        <v>95.14</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>1062</v>
+        <v>1147.86</v>
       </c>
       <c r="K11" s="16">
         <f>IFERROR(H11/G11,"")</f>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="L11" s="12" t="n"/>
       <c r="M11" s="17" t="n">
-        <v>46268</v>
+        <v>46295</v>
       </c>
       <c r="N11" s="5" t="inlineStr">
         <is>
@@ -1866,11 +1866,11 @@
         <v>0.92</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>1BR — group floor (lowest listing); the lowest-five measure was not provided</t>
+          <t>1BR — lowest five of 10 available</t>
         </is>
       </c>
       <c r="E12" s="15" t="n">
@@ -1881,13 +1881,13 @@
         <v>658</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>1044</v>
+        <v>1042.6</v>
       </c>
       <c r="I12" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>1044</v>
+        <v>1042.6</v>
       </c>
       <c r="K12" s="16">
         <f>IFERROR(H12/G12,"")</f>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="L12" s="12" t="n"/>
       <c r="M12" s="17" t="n">
-        <v>46267</v>
+        <v>46294</v>
       </c>
       <c r="N12" s="5" t="inlineStr">
         <is>
@@ -1906,18 +1906,18 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Gilbert Greens Apartments</t>
+          <t>Lucera Apartments</t>
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>1.63</v>
+        <v>1.46</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>1BR — group floor (lowest listing); the lowest-five measure was not provided</t>
+          <t>1BR — lowest five of 2 available</t>
         </is>
       </c>
       <c r="E13" s="15" t="n">
@@ -1925,16 +1925,16 @@
       </c>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="7" t="n">
-        <v>605</v>
+        <v>530</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>1250</v>
+        <v>1109</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>1202</v>
+        <v>1109</v>
       </c>
       <c r="K13" s="16">
         <f>IFERROR(H13/G13,"")</f>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L13" s="12" t="n"/>
       <c r="M13" s="17" t="n">
-        <v>46267</v>
+        <v>46295</v>
       </c>
       <c r="N13" s="5" t="inlineStr">
         <is>
@@ -1953,35 +1953,35 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Gilbert Greens Apartments</t>
+          <t>Lucera Apartments</t>
         </is>
       </c>
       <c r="B14" s="10" t="n">
-        <v>1.63</v>
+        <v>1.46</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>2BR — group floor (lowest listing); the lowest-five measure was not provided</t>
+          <t>1BR — lowest five of 4 available</t>
         </is>
       </c>
       <c r="E14" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" s="12" t="n"/>
       <c r="G14" s="7" t="n">
-        <v>808</v>
+        <v>700</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>1425</v>
+        <v>1244.25</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>1370</v>
+        <v>1244.25</v>
       </c>
       <c r="K14" s="16">
         <f>IFERROR(H14/G14,"")</f>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="L14" s="12" t="n"/>
       <c r="M14" s="17" t="n">
-        <v>46267</v>
+        <v>46295</v>
       </c>
       <c r="N14" s="5" t="inlineStr">
         <is>
@@ -1997,170 +1997,170 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Tier 2 — Additional comps: the next 5 communities matching the subject's product and vintage</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
-    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Lucera Apartments</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>1986</v>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>2BR — lowest five of 6 available</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" s="12" t="n"/>
+      <c r="G15" s="7" t="n">
+        <v>892</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>1413</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="7" t="n">
+        <v>1413</v>
+      </c>
+      <c r="K15" s="16">
+        <f>IFERROR(H15/G15,"")</f>
+        <v/>
+      </c>
+      <c r="L15" s="12" t="n"/>
+      <c r="M15" s="17" t="n">
+        <v>46295</v>
+      </c>
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>own weekly scrape</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Tier 2 — Additional comps: the next 8 communities matching the subject's product and vintage</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>Community</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>Distance (mi)</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C18" s="14" t="inlineStr">
         <is>
           <t>Year built</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>Floor plan</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E18" s="14" t="inlineStr">
         <is>
           <t>Beds</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="F18" s="14" t="inlineStr">
         <is>
           <t>Baths</t>
         </is>
       </c>
-      <c r="G17" s="14" t="inlineStr">
+      <c r="G18" s="14" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="H17" s="14" t="inlineStr">
+      <c r="H18" s="14" t="inlineStr">
         <is>
           <t>Asking rent</t>
         </is>
       </c>
-      <c r="I17" s="14" t="inlineStr">
+      <c r="I18" s="14" t="inlineStr">
         <is>
           <t>Concession</t>
         </is>
       </c>
-      <c r="J17" s="14" t="inlineStr">
+      <c r="J18" s="14" t="inlineStr">
         <is>
           <t>Net effective rent</t>
         </is>
       </c>
-      <c r="K17" s="14" t="inlineStr">
+      <c r="K18" s="14" t="inlineStr">
         <is>
           <t>Asking $/SF</t>
         </is>
       </c>
-      <c r="L17" s="14" t="inlineStr">
+      <c r="L18" s="14" t="inlineStr">
         <is>
           <t>Occupancy</t>
         </is>
       </c>
-      <c r="M17" s="14" t="inlineStr">
+      <c r="M18" s="14" t="inlineStr">
         <is>
           <t>As-of date</t>
         </is>
       </c>
-      <c r="N17" s="14" t="inlineStr">
+      <c r="N18" s="14" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Mesa Station</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="C18" s="8" t="n">
-        <v>1984</v>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>1BR — group floor (lowest listing); the lowest-five measure was not provided</t>
-        </is>
-      </c>
-      <c r="E18" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="12" t="n"/>
-      <c r="G18" s="7" t="n">
-        <v>570</v>
-      </c>
-      <c r="H18" s="7" t="n">
-        <v>908</v>
-      </c>
-      <c r="I18" s="7" t="n">
-        <v>70</v>
-      </c>
-      <c r="J18" s="7" t="n">
-        <v>838</v>
-      </c>
-      <c r="K18" s="16">
-        <f>IFERROR(H18/G18,"")</f>
-        <v/>
-      </c>
-      <c r="L18" s="12" t="n"/>
-      <c r="M18" s="17" t="n">
-        <v>46267</v>
-      </c>
-      <c r="N18" s="5" t="inlineStr">
-        <is>
-          <t>own weekly scrape</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Mesa Station</t>
+          <t>Pebble Creek</t>
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="C19" s="8" t="n">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>2BR — group floor (lowest listing); the lowest-five measure was not provided</t>
+          <t>1BR — lowest five of 1 available</t>
         </is>
       </c>
       <c r="E19" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" s="12" t="n"/>
       <c r="G19" s="7" t="n">
-        <v>686</v>
+        <v>630</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>1000</v>
+        <v>1150</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>923</v>
+        <v>1150</v>
       </c>
       <c r="K19" s="16">
         <f>IFERROR(H19/G19,"")</f>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="L19" s="12" t="n"/>
       <c r="M19" s="17" t="n">
-        <v>46267</v>
+        <v>46295</v>
       </c>
       <c r="N19" s="5" t="inlineStr">
         <is>
@@ -2179,18 +2179,18 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Mesa Station</t>
+          <t>Pebble Creek</t>
         </is>
       </c>
       <c r="B20" s="10" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="C20" s="8" t="n">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>2BR — group floor (lowest listing); the lowest-five measure was not provided</t>
+          <t>2BR — lowest five of 1 available</t>
         </is>
       </c>
       <c r="E20" s="15" t="n">
@@ -2198,16 +2198,16 @@
       </c>
       <c r="F20" s="12" t="n"/>
       <c r="G20" s="7" t="n">
-        <v>771</v>
+        <v>780</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>1186</v>
+        <v>1425</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>1095</v>
+        <v>1425</v>
       </c>
       <c r="K20" s="16">
         <f>IFERROR(H20/G20,"")</f>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="L20" s="12" t="n"/>
       <c r="M20" s="17" t="n">
-        <v>46267</v>
+        <v>46295</v>
       </c>
       <c r="N20" s="5" t="inlineStr">
         <is>
@@ -2226,18 +2226,18 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Dana Park Apartments</t>
+          <t>Gilbert Greens Apartments</t>
         </is>
       </c>
       <c r="B21" s="10" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="C21" s="8" t="n">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>1BR — group floor (lowest listing); the lowest-five measure was not provided</t>
+          <t>1BR — lowest five of 5 available</t>
         </is>
       </c>
       <c r="E21" s="15" t="n">
@@ -2245,16 +2245,16 @@
       </c>
       <c r="F21" s="12" t="n"/>
       <c r="G21" s="7" t="n">
-        <v>722</v>
+        <v>605</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>1245</v>
+        <v>1230</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>239</v>
+        <v>94.3</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>1006</v>
+        <v>1135.7</v>
       </c>
       <c r="K21" s="16">
         <f>IFERROR(H21/G21,"")</f>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="L21" s="12" t="n"/>
       <c r="M21" s="17" t="n">
-        <v>46268</v>
+        <v>46294</v>
       </c>
       <c r="N21" s="5" t="inlineStr">
         <is>
@@ -2273,18 +2273,18 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Dana Park Apartments</t>
+          <t>Gilbert Greens Apartments</t>
         </is>
       </c>
       <c r="B22" s="10" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="C22" s="8" t="n">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>2BR — group floor (lowest listing); the lowest-five measure was not provided</t>
+          <t>2BR — lowest five of 1 available</t>
         </is>
       </c>
       <c r="E22" s="15" t="n">
@@ -2292,16 +2292,16 @@
       </c>
       <c r="F22" s="12" t="n"/>
       <c r="G22" s="7" t="n">
-        <v>1025</v>
+        <v>808</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>1499</v>
+        <v>1425</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>288</v>
+        <v>110</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>1211</v>
+        <v>1315</v>
       </c>
       <c r="K22" s="16">
         <f>IFERROR(H22/G22,"")</f>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="L22" s="12" t="n"/>
       <c r="M22" s="17" t="n">
-        <v>46268</v>
+        <v>46294</v>
       </c>
       <c r="N22" s="5" t="inlineStr">
         <is>
@@ -2320,35 +2320,35 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Dana Park Apartments</t>
+          <t>Mesa Station</t>
         </is>
       </c>
       <c r="B23" s="10" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="C23" s="8" t="n">
-        <v>1986</v>
+        <v>1984</v>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>2BR — group floor (lowest listing); the lowest-five measure was not provided</t>
+          <t>1BR — lowest five of 12 available</t>
         </is>
       </c>
       <c r="E23" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23" s="12" t="n"/>
       <c r="G23" s="7" t="n">
-        <v>1067</v>
+        <v>570</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>1645</v>
+        <v>953.2</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>316</v>
+        <v>0</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>1329</v>
+        <v>953.2</v>
       </c>
       <c r="K23" s="16">
         <f>IFERROR(H23/G23,"")</f>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="L23" s="12" t="n"/>
       <c r="M23" s="17" t="n">
-        <v>46268</v>
+        <v>46294</v>
       </c>
       <c r="N23" s="5" t="inlineStr">
         <is>
@@ -2367,35 +2367,35 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Astero Mesa East</t>
+          <t>Mesa Station</t>
         </is>
       </c>
       <c r="B24" s="10" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="C24" s="8" t="n">
-        <v>1987</v>
+        <v>1984</v>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>1BR — group floor (lowest listing); the lowest-five measure was not provided</t>
+          <t>2BR — lowest five of 29 available</t>
         </is>
       </c>
       <c r="E24" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24" s="12" t="n"/>
       <c r="G24" s="7" t="n">
-        <v>700</v>
+        <v>686</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>1249</v>
+        <v>990.2</v>
       </c>
       <c r="I24" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>1249</v>
+        <v>990.2</v>
       </c>
       <c r="K24" s="16">
         <f>IFERROR(H24/G24,"")</f>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="L24" s="12" t="n"/>
       <c r="M24" s="17" t="n">
-        <v>46267</v>
+        <v>46294</v>
       </c>
       <c r="N24" s="5" t="inlineStr">
         <is>
@@ -2414,18 +2414,18 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Astero Mesa East</t>
+          <t>Mesa Station</t>
         </is>
       </c>
       <c r="B25" s="10" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="C25" s="8" t="n">
-        <v>1987</v>
+        <v>1984</v>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>2BR — group floor (lowest listing); the lowest-five measure was not provided</t>
+          <t>2BR — lowest five of 8 available</t>
         </is>
       </c>
       <c r="E25" s="15" t="n">
@@ -2433,16 +2433,16 @@
       </c>
       <c r="F25" s="12" t="n"/>
       <c r="G25" s="7" t="n">
-        <v>900</v>
+        <v>771</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>1449</v>
+        <v>1130</v>
       </c>
       <c r="I25" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>1449</v>
+        <v>1130</v>
       </c>
       <c r="K25" s="16">
         <f>IFERROR(H25/G25,"")</f>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="L25" s="12" t="n"/>
       <c r="M25" s="17" t="n">
-        <v>46267</v>
+        <v>46294</v>
       </c>
       <c r="N25" s="5" t="inlineStr">
         <is>
@@ -2461,35 +2461,35 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Astero Mesa East</t>
+          <t>Dana Park Apartments</t>
         </is>
       </c>
       <c r="B26" s="10" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="C26" s="8" t="n">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>2BR — group floor (lowest listing); the lowest-five measure was not provided</t>
+          <t>1BR — lowest five of 1 available</t>
         </is>
       </c>
       <c r="E26" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26" s="12" t="n"/>
       <c r="G26" s="7" t="n">
-        <v>1044</v>
+        <v>722</v>
       </c>
       <c r="H26" s="7" t="n">
-        <v>1499</v>
+        <v>1245</v>
       </c>
       <c r="I26" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>1499</v>
+        <v>1245</v>
       </c>
       <c r="K26" s="16">
         <f>IFERROR(H26/G26,"")</f>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="L26" s="12" t="n"/>
       <c r="M26" s="17" t="n">
-        <v>46267</v>
+        <v>46295</v>
       </c>
       <c r="N26" s="5" t="inlineStr">
         <is>
@@ -2508,35 +2508,35 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Astero Mesa West</t>
+          <t>Dana Park Apartments</t>
         </is>
       </c>
       <c r="B27" s="10" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="C27" s="8" t="n">
         <v>1986</v>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>1BR — group floor (lowest listing); the lowest-five measure was not provided</t>
+          <t>2BR — lowest five of 1 available</t>
         </is>
       </c>
       <c r="E27" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="12" t="n"/>
       <c r="G27" s="7" t="n">
-        <v>576</v>
+        <v>1025</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>1049</v>
+        <v>1599</v>
       </c>
       <c r="I27" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>1049</v>
+        <v>1599</v>
       </c>
       <c r="K27" s="16">
         <f>IFERROR(H27/G27,"")</f>
@@ -2544,7 +2544,7 @@
       </c>
       <c r="L27" s="12" t="n"/>
       <c r="M27" s="17" t="n">
-        <v>46268</v>
+        <v>46295</v>
       </c>
       <c r="N27" s="5" t="inlineStr">
         <is>
@@ -2555,18 +2555,18 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Astero Mesa West</t>
+          <t>Dana Park Apartments</t>
         </is>
       </c>
       <c r="B28" s="10" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="C28" s="8" t="n">
         <v>1986</v>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>2BR — group floor (lowest listing); the lowest-five measure was not provided</t>
+          <t>2BR — lowest five of 1 available</t>
         </is>
       </c>
       <c r="E28" s="15" t="n">
@@ -2574,16 +2574,16 @@
       </c>
       <c r="F28" s="12" t="n"/>
       <c r="G28" s="7" t="n">
-        <v>1035</v>
+        <v>1067</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>1349</v>
+        <v>1695</v>
       </c>
       <c r="I28" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>1349</v>
+        <v>1695</v>
       </c>
       <c r="K28" s="16">
         <f>IFERROR(H28/G28,"")</f>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="L28" s="12" t="n"/>
       <c r="M28" s="17" t="n">
-        <v>46268</v>
+        <v>46295</v>
       </c>
       <c r="N28" s="5" t="inlineStr">
         <is>
@@ -2602,35 +2602,35 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Gentrys Walk Apartments</t>
+          <t>Astero Mesa East</t>
         </is>
       </c>
       <c r="B29" s="10" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="C29" s="8" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>1BR — group floor (lowest listing); the lowest-five measure was not provided</t>
+          <t>2BR — lowest five of 1 available</t>
         </is>
       </c>
       <c r="E29" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" s="12" t="n"/>
       <c r="G29" s="7" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>1212</v>
+        <v>1399</v>
       </c>
       <c r="I29" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>1212</v>
+        <v>1399</v>
       </c>
       <c r="K29" s="16">
         <f>IFERROR(H29/G29,"")</f>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="L29" s="12" t="n"/>
       <c r="M29" s="17" t="n">
-        <v>46268</v>
+        <v>46294</v>
       </c>
       <c r="N29" s="5" t="inlineStr">
         <is>
@@ -2646,358 +2646,1074 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Astero Mesa East</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C30" s="8" t="n">
+        <v>1987</v>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>2BR — lowest five of 1 available</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" s="12" t="n"/>
+      <c r="G30" s="7" t="n">
+        <v>1044</v>
+      </c>
+      <c r="H30" s="7" t="n">
+        <v>1449</v>
+      </c>
+      <c r="I30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="7" t="n">
+        <v>1449</v>
+      </c>
+      <c r="K30" s="16">
+        <f>IFERROR(H30/G30,"")</f>
+        <v/>
+      </c>
+      <c r="L30" s="12" t="n"/>
+      <c r="M30" s="17" t="n">
+        <v>46294</v>
+      </c>
+      <c r="N30" s="5" t="inlineStr">
+        <is>
+          <t>own weekly scrape</t>
+        </is>
+      </c>
+    </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>By bed count — like for like</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="n"/>
-      <c r="C31" s="4" t="n"/>
-      <c r="D31" s="4" t="n"/>
-      <c r="E31" s="4" t="n"/>
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Astero Mesa West</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="C31" s="8" t="n">
+        <v>1986</v>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>1BR — lowest five of 1 available — STALE snapshot (older than the tracker's freshness threshold)</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="12" t="n"/>
+      <c r="G31" s="7" t="n">
+        <v>576</v>
+      </c>
+      <c r="H31" s="7" t="n">
+        <v>1049</v>
+      </c>
+      <c r="I31" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="7" t="n">
+        <v>1049</v>
+      </c>
+      <c r="K31" s="16">
+        <f>IFERROR(H31/G31,"")</f>
+        <v/>
+      </c>
+      <c r="L31" s="12" t="n"/>
+      <c r="M31" s="17" t="n">
+        <v>46281</v>
+      </c>
+      <c r="N31" s="5" t="inlineStr">
+        <is>
+          <t>own weekly scrape</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="14" t="inlineStr">
-        <is>
-          <t>Beds</t>
-        </is>
-      </c>
-      <c r="B32" s="14" t="inlineStr">
-        <is>
-          <t>Communities</t>
-        </is>
-      </c>
-      <c r="C32" s="14" t="inlineStr">
-        <is>
-          <t>Plans</t>
-        </is>
-      </c>
-      <c r="D32" s="14" t="inlineStr">
-        <is>
-          <t>Avg asking</t>
-        </is>
-      </c>
-      <c r="E32" s="14" t="inlineStr">
-        <is>
-          <t>Avg net effective</t>
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Gentrys Walk Apartments</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="C32" s="8" t="n">
+        <v>1986</v>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>1BR — lowest five of 6 available</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="12" t="n"/>
+      <c r="G32" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="H32" s="7" t="n">
+        <v>1226.6</v>
+      </c>
+      <c r="I32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="7" t="n">
+        <v>1226.6</v>
+      </c>
+      <c r="K32" s="16">
+        <f>IFERROR(H32/G32,"")</f>
+        <v/>
+      </c>
+      <c r="L32" s="12" t="n"/>
+      <c r="M32" s="17" t="n">
+        <v>46295</v>
+      </c>
+      <c r="N32" s="5" t="inlineStr">
+        <is>
+          <t>own weekly scrape</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>1 bed</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="C33" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="D33" s="7" t="n">
-        <v>1118.3</v>
-      </c>
-      <c r="E33" s="7" t="n">
-        <v>1068.7</v>
+          <t>Gentrys Walk Apartments</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="C33" s="8" t="n">
+        <v>1986</v>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>1BR — lowest five of 4 available</t>
+        </is>
+      </c>
+      <c r="E33" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="12" t="n"/>
+      <c r="G33" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="H33" s="7" t="n">
+        <v>1344.5</v>
+      </c>
+      <c r="I33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="7" t="n">
+        <v>1344.5</v>
+      </c>
+      <c r="K33" s="16">
+        <f>IFERROR(H33/G33,"")</f>
+        <v/>
+      </c>
+      <c r="L33" s="12" t="n"/>
+      <c r="M33" s="17" t="n">
+        <v>46295</v>
+      </c>
+      <c r="N33" s="5" t="inlineStr">
+        <is>
+          <t>own weekly scrape</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>2 bed</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C34" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="D34" s="7" t="n">
-        <v>1373.111111111111</v>
-      </c>
-      <c r="E34" s="7" t="n">
-        <v>1281.222222222222</v>
-      </c>
-    </row>
-    <row r="35"/>
+          <t>Gentrys Walk Apartments</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="C34" s="8" t="n">
+        <v>1986</v>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>2BR — lowest five of 8 available</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" s="12" t="n"/>
+      <c r="G34" s="7" t="n">
+        <v>920</v>
+      </c>
+      <c r="H34" s="7" t="n">
+        <v>1432.4</v>
+      </c>
+      <c r="I34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="7" t="n">
+        <v>1432.4</v>
+      </c>
+      <c r="K34" s="16">
+        <f>IFERROR(H34/G34,"")</f>
+        <v/>
+      </c>
+      <c r="L34" s="12" t="n"/>
+      <c r="M34" s="17" t="n">
+        <v>46295</v>
+      </c>
+      <c r="N34" s="5" t="inlineStr">
+        <is>
+          <t>own weekly scrape</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>The Orchard on Gilbert</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="C35" s="8" t="n">
+        <v>1986</v>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>1BR — lowest five of 14 available</t>
+        </is>
+      </c>
+      <c r="E35" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="12" t="n"/>
+      <c r="G35" s="7" t="n">
+        <v>483</v>
+      </c>
+      <c r="H35" s="7" t="n">
+        <v>1209.4</v>
+      </c>
+      <c r="I35" s="7" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="J35" s="7" t="n">
+        <v>1116.6</v>
+      </c>
+      <c r="K35" s="16">
+        <f>IFERROR(H35/G35,"")</f>
+        <v/>
+      </c>
+      <c r="L35" s="12" t="n"/>
+      <c r="M35" s="17" t="n">
+        <v>46295</v>
+      </c>
+      <c r="N35" s="5" t="inlineStr">
+        <is>
+          <t>own weekly scrape</t>
+        </is>
+      </c>
+    </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>Subject versus comp set — detailed tiers only</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="n"/>
-      <c r="C36" s="4" t="n"/>
-      <c r="D36" s="4" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>Subject market rent</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="n">
-        <v>1344.6</v>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>Unit-weighted market rent for model, whole property.</t>
-        </is>
-      </c>
-    </row>
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>The Orchard on Gilbert</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="C36" s="8" t="n">
+        <v>1986</v>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>2BR — lowest five of 3 available</t>
+        </is>
+      </c>
+      <c r="E36" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" s="12" t="n"/>
+      <c r="G36" s="7" t="n">
+        <v>865</v>
+      </c>
+      <c r="H36" s="7" t="n">
+        <v>1585</v>
+      </c>
+      <c r="I36" s="7" t="n">
+        <v>121.84</v>
+      </c>
+      <c r="J36" s="7" t="n">
+        <v>1463.16</v>
+      </c>
+      <c r="K36" s="16">
+        <f>IFERROR(H36/G36,"")</f>
+        <v/>
+      </c>
+      <c r="L36" s="12" t="n"/>
+      <c r="M36" s="17" t="n">
+        <v>46295</v>
+      </c>
+      <c r="N36" s="5" t="inlineStr">
+        <is>
+          <t>own weekly scrape</t>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>Comp-set average asking</t>
-        </is>
-      </c>
-      <c r="B38" s="7">
-        <f>IFERROR(AVERAGE(H8:H14,H18:H29),"")</f>
-        <v/>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>Over 10 communities in the detailed tiers (top 5 plus next 15) — never the whole radius.</t>
-        </is>
-      </c>
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Unit count and year built, by community — each with its source</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="n"/>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="4" t="n"/>
+      <c r="F38" s="4" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>Comp-set average net effective</t>
-        </is>
-      </c>
-      <c r="B39" s="7">
-        <f>IFERROR(AVERAGE(J8:J14,J18:J29),"")</f>
-        <v/>
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>Community</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="D39" s="14" t="inlineStr">
+        <is>
+          <t>Units from</t>
+        </is>
+      </c>
+      <c r="E39" s="14" t="inlineStr">
+        <is>
+          <t>Year built</t>
+        </is>
+      </c>
+      <c r="F39" s="14" t="inlineStr">
+        <is>
+          <t>Year built from</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Comp set, mix-matched</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="n">
-        <v>1172.943495077356</v>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>Each bed count's comp net-effective weighted by the subject's own unit mix, so both sides describe the same product.</t>
+          <t>Saltera Apartments</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>306</v>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>1984</v>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>Subject rent, same bed counts</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="n">
-        <v>1314.301989343287</v>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>Restricted to the bed counts the comp set covers: [1, 2].</t>
+          <t>The Hamptons</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" s="7" t="n">
+        <v>249</v>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>1981</v>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>Mix coverage</t>
-        </is>
-      </c>
-      <c r="B42" s="11" t="n">
-        <v>0.9461077844311377</v>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>Share of the subject's units actually compared, by bed count and priced plan.</t>
+          <t>Cielo on Gilbert</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" s="7" t="n">
+        <v>432</v>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>1985</v>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>Subject vs comp set (mix-matched)</t>
-        </is>
-      </c>
-      <c r="B43" s="11">
-        <f>IFERROR(B41/B40-1,"")</f>
-        <v/>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>Negative means the subject is underwritten BELOW the market — mark-to-market room rather than a stretch.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44"/>
+          <t>The Vance</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="7" t="n">
+        <v>464</v>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>1986</v>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>Lucera Apartments</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" s="7" t="n">
+        <v>192</v>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>1986</v>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
+        </is>
+      </c>
+    </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>Two comp sets, selected identically except for the vintage test</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="n"/>
-      <c r="C45" s="4" t="n"/>
-      <c r="D45" s="4" t="n"/>
-      <c r="E45" s="4" t="n"/>
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>Pebble Creek</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C45" s="7" t="n">
+        <v>122</v>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>1985</v>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>Held fixed in both: candidate pool, product test, tracker comp exclusions, radius, closest-20 cap, per-community rent rules, mix weighting. Varied: the +/-10-year vintage test only.</t>
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>Gilbert Greens Apartments</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C46" s="7" t="n">
+        <v>164</v>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>1985</v>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="14" t="inlineStr">
-        <is>
-          <t>Comp set</t>
-        </is>
-      </c>
-      <c r="B47" s="14" t="inlineStr">
-        <is>
-          <t>Communities</t>
-        </is>
-      </c>
-      <c r="C47" s="14" t="inlineStr">
-        <is>
-          <t>Vintages</t>
-        </is>
-      </c>
-      <c r="D47" s="14" t="inlineStr">
-        <is>
-          <t>Comp net effective</t>
-        </is>
-      </c>
-      <c r="E47" s="14" t="inlineStr">
-        <is>
-          <t>Subject reads</t>
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>Mesa Station</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" s="7" t="n">
+        <v>397</v>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>1984</v>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>A — vintage test ON</t>
-        </is>
-      </c>
-      <c r="B48" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>1981–1987</t>
-        </is>
-      </c>
-      <c r="D48" s="7" t="n">
-        <v>1172.943495077356</v>
-      </c>
-      <c r="E48" s="11" t="n">
-        <v>0.1205160307032596</v>
+          <t>Dana Park Apartments</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C48" s="7" t="n">
+        <v>222</v>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>1986</v>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>B — vintage test OFF</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="n">
-        <v>13</v>
+          <t>Astero Mesa East</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="n">
+        <v>2</v>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>1981–2018</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="n">
-        <v>1217.446518987342</v>
-      </c>
-      <c r="E49" s="11" t="n">
-        <v>0.07955624238550407</v>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>No public record; the licensed count is held back</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="n">
+        <v>1987</v>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>community registry (third-party market data)</t>
+        </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="18" t="inlineStr">
-        <is>
-          <t>Difference between the two sets</t>
-        </is>
-      </c>
-      <c r="B50" s="19" t="n"/>
-      <c r="C50" s="19" t="n"/>
-      <c r="D50" s="20" t="n">
-        <v>44.50302390998604</v>
-      </c>
-      <c r="E50" s="21" t="n">
-        <v>0.04095978831775549</v>
-      </c>
-    </row>
-    <row r="51"/>
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>Astero Mesa West</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>No public record; the licensed count is held back</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="n">
+        <v>1986</v>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>community registry (third-party market data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>Gentrys Walk Apartments</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C51" s="7" t="n">
+        <v>176</v>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>1986</v>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
+        </is>
+      </c>
+    </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
+          <t>The Orchard on Gilbert</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C52" s="7" t="n">
+        <v>130</v>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="n">
+        <v>1986</v>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="53"/>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>By bed count — like for like</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="n"/>
+      <c r="C54" s="4" t="n"/>
+      <c r="D54" s="4" t="n"/>
+      <c r="E54" s="4" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="14" t="inlineStr">
+        <is>
+          <t>Beds</t>
+        </is>
+      </c>
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t>Communities</t>
+        </is>
+      </c>
+      <c r="C55" s="14" t="inlineStr">
+        <is>
+          <t>Plans</t>
+        </is>
+      </c>
+      <c r="D55" s="14" t="inlineStr">
+        <is>
+          <t>Avg asking</t>
+        </is>
+      </c>
+      <c r="E55" s="14" t="inlineStr">
+        <is>
+          <t>Avg net effective</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>1 bed</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="C56" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>1160.167857142857</v>
+      </c>
+      <c r="E56" s="7" t="n">
+        <v>1140.007857142857</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>2 bed</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C57" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>1394.05</v>
+      </c>
+      <c r="E57" s="7" t="n">
+        <v>1374.73</v>
+      </c>
+    </row>
+    <row r="58"/>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>Subject versus comp set — detailed tiers only</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="n"/>
+      <c r="C59" s="4" t="n"/>
+      <c r="D59" s="4" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>Subject market rent</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="n">
+        <v>1344.6</v>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>Unit-weighted market rent for model, whole property.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>Comp-set average asking</t>
+        </is>
+      </c>
+      <c r="B61" s="7">
+        <f>IFERROR(AVERAGE(H8:H15,H19:H36),"")</f>
+        <v/>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>Over 13 communities in the detailed tiers (top 5 plus next 15) — never the whole radius.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>Comp-set average net effective</t>
+        </is>
+      </c>
+      <c r="B62" s="7">
+        <f>IFERROR(AVERAGE(J8:J15,J19:J36),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>Comp set, mix-matched</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="n">
+        <v>1255.140553797469</v>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>Each bed count's comp net-effective weighted by the subject's own unit mix, so both sides describe the same product.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>Subject rent, same bed counts</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="n">
+        <v>1314.301989343287</v>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>Restricted to the bed counts the comp set covers: [1, 2].</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>Mix coverage</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="n">
+        <v>0.9461077844311377</v>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>Share of the subject's units actually compared, by bed count and priced plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>Subject vs comp set (mix-matched)</t>
+        </is>
+      </c>
+      <c r="B66" s="11">
+        <f>IFERROR(B64/B63-1,"")</f>
+        <v/>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>Negative means the subject is underwritten BELOW the market — mark-to-market room rather than a stretch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67"/>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>Two comp sets, selected identically except for the vintage test</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="n"/>
+      <c r="C68" s="4" t="n"/>
+      <c r="D68" s="4" t="n"/>
+      <c r="E68" s="4" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>Held fixed in both: candidate pool, product test, tracker comp exclusions, radius, closest-20 cap, per-community rent rules, mix weighting. Varied: the +/-10-year vintage test only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="14" t="inlineStr">
+        <is>
+          <t>Comp set</t>
+        </is>
+      </c>
+      <c r="B70" s="14" t="inlineStr">
+        <is>
+          <t>Communities</t>
+        </is>
+      </c>
+      <c r="C70" s="14" t="inlineStr">
+        <is>
+          <t>Vintages</t>
+        </is>
+      </c>
+      <c r="D70" s="14" t="inlineStr">
+        <is>
+          <t>Comp net effective</t>
+        </is>
+      </c>
+      <c r="E70" s="14" t="inlineStr">
+        <is>
+          <t>Subject reads</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>A — vintage test ON</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>1981–1987</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="n">
+        <v>1255.140553797469</v>
+      </c>
+      <c r="E71" s="11" t="n">
+        <v>0.04713530717083714</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>B — vintage test OFF</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>1981–2018</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="n">
+        <v>1303.423449367089</v>
+      </c>
+      <c r="E72" s="11" t="n">
+        <v>0.008346128789903817</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="18" t="inlineStr">
+        <is>
+          <t>Difference between the two sets</t>
+        </is>
+      </c>
+      <c r="B73" s="19" t="n"/>
+      <c r="C73" s="19" t="n"/>
+      <c r="D73" s="20" t="n">
+        <v>48.28289556962</v>
+      </c>
+      <c r="E73" s="21" t="n">
+        <v>0.03878917838093332</v>
+      </c>
+    </row>
+    <row r="74"/>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
           <t>In B but not A</t>
         </is>
       </c>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>Lindsay Palms Apartments, The Premiere at Dana Park, Vista Grove</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>Craft at Gilbert and Baseline, The Premiere at Dana Park, The Village at Lindsay Park Apartments, Vista Grove</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
         <is>
           <t>In A but not B</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
         <is>
           <t>Both figures are weighted by this property's own unit mix and computed over the same bed counts, so the two rows describe the same product. This is what these two sets measured on this date; it is not an estimate of what vintage is worth in this market.</t>
         </is>
       </c>
     </row>
-    <row r="55"/>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+    <row r="78"/>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t>Stated in the offering memorandum</t>
         </is>
       </c>
-      <c r="B56" s="4" t="n"/>
-      <c r="C56" s="4" t="n"/>
-      <c r="D56" s="4" t="n"/>
-      <c r="E56" s="4" t="n"/>
-      <c r="F56" s="4" t="n"/>
-      <c r="G56" s="4" t="n"/>
-      <c r="H56" s="4" t="n"/>
-      <c r="I56" s="4" t="n"/>
-      <c r="J56" s="4" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="B79" s="4" t="n"/>
+      <c r="C79" s="4" t="n"/>
+      <c r="D79" s="4" t="n"/>
+      <c r="E79" s="4" t="n"/>
+      <c r="F79" s="4" t="n"/>
+      <c r="G79" s="4" t="n"/>
+      <c r="H79" s="4" t="n"/>
+      <c r="I79" s="4" t="n"/>
+      <c r="J79" s="4" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>The memorandum's stated comparables are withheld: they would place the real asset.</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="6" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>Retail for-sale comps are not part of this demo. Sale comparables shown here are the whole-community trades the memorandum itself cites.</t>
         </is>
@@ -3620,16 +4336,16 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>7205.408782354566</v>
+        <v>7205.769022616706</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>56132.3904975113</v>
+        <v>56132.49059874286</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>146225.0843639599</v>
+        <v>146226.2857280746</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>419520.7372023506</v>
+        <v>419524.3564018827</v>
       </c>
       <c r="F10" s="7" t="n">
         <v>1790242</v>
@@ -3654,10 +4370,10 @@
         <v>58574</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>150543</v>
+        <v>150544</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>437696</v>
+        <v>437699</v>
       </c>
       <c r="F11" s="7" t="n">
         <v>1892613</v>
@@ -3676,16 +4392,16 @@
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>0.07016829064349328</v>
+        <v>0.07011478938577254</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>0.04349733693591684</v>
+        <v>0.0434954760641213</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>0.02952924017668956</v>
+        <v>0.02952762049878443</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>0.0433238721853284</v>
+        <v>0.04332202247801553</v>
       </c>
       <c r="F12" s="11" t="n">
         <v>0.05718277193809551</v>
@@ -3731,10 +4447,10 @@
         <v>61239.48308749999</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>157393.64739375</v>
+        <v>157394.6929</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>457613.9036</v>
+        <v>457617.04011875</v>
       </c>
       <c r="F14" s="7" t="n">
         <v>1978738.72033125</v>
@@ -3805,16 +4521,16 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>20710</v>
+        <v>20712</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>155942</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>393000</v>
+        <v>393001</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>1100029</v>
+        <v>1100032</v>
       </c>
       <c r="F18" s="7" t="n">
         <v>4845832</v>
@@ -3833,7 +4549,7 @@
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>20297</v>
+        <v>20298</v>
       </c>
       <c r="C19" s="7" t="n">
         <v>159356</v>
@@ -3842,7 +4558,7 @@
         <v>394900</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>1119327</v>
+        <v>1119329</v>
       </c>
       <c r="F19" s="7" t="n">
         <v>5028754</v>
@@ -3861,16 +4577,16 @@
         </is>
       </c>
       <c r="B20" s="11" t="n">
-        <v>-0.01994205697730567</v>
+        <v>-0.01998841251448435</v>
       </c>
       <c r="C20" s="11" t="n">
         <v>0.0218927549986534</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>0.004834605597964448</v>
+        <v>0.004832048773412811</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.01754317386177995</v>
+        <v>0.01754221695368852</v>
       </c>
       <c r="F20" s="11" t="n">
         <v>0.03774831649136834</v>
@@ -3910,7 +4626,7 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>20745.989937</v>
+        <v>20747.012058</v>
       </c>
       <c r="C22" s="7" t="n">
         <v>162881.114076</v>
@@ -3919,7 +4635,7 @@
         <v>403635.5828999999</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>1144087.632567</v>
+        <v>1144089.676809</v>
       </c>
       <c r="F22" s="7" t="n">
         <v>5139995.067233999</v>
@@ -4003,7 +4719,7 @@
         <v>6243</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>17153</v>
+        <v>17154</v>
       </c>
       <c r="E27" s="7" t="n">
         <v>47798</v>
@@ -4031,10 +4747,10 @@
         <v>10719</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>25455</v>
+        <v>25456</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>64599</v>
+        <v>64600</v>
       </c>
       <c r="F28" s="7" t="n">
         <v>288010</v>
@@ -4053,7 +4769,7 @@
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="C29" s="7" t="n">
         <v>10649</v>
@@ -4062,7 +4778,7 @@
         <v>25949</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>70655</v>
+        <v>70656</v>
       </c>
       <c r="F29" s="7" t="n">
         <v>302932</v>
@@ -4115,10 +4831,10 @@
         <v>7376</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>16579</v>
+        <v>16580</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>51719</v>
+        <v>51720</v>
       </c>
       <c r="F31" s="7" t="n">
         <v>217512</v>
@@ -4143,7 +4859,7 @@
         <v>4953</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>12640</v>
+        <v>12641</v>
       </c>
       <c r="E32" s="7" t="n">
         <v>38937</v>
@@ -4165,13 +4881,13 @@
         </is>
       </c>
       <c r="B33" s="7" t="n">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>5032</v>
+        <v>5031</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>14857</v>
+        <v>14856</v>
       </c>
       <c r="E33" s="7" t="n">
         <v>47604</v>
@@ -4224,13 +4940,13 @@
         <v>5566</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>41613</v>
+        <v>41612</v>
       </c>
       <c r="D35" s="7" t="n">
         <v>107934</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>325299</v>
+        <v>325301</v>
       </c>
       <c r="F35" s="7" t="n">
         <v>1393097</v>
@@ -4283,7 +4999,7 @@
         <v>22337</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>60138</v>
+        <v>60137</v>
       </c>
       <c r="E37" s="7" t="n">
         <v>193645</v>
@@ -4392,13 +5108,13 @@
         </is>
       </c>
       <c r="B43" s="7" t="n">
-        <v>94565</v>
+        <v>94562</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>98600</v>
+        <v>98599</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>105369</v>
+        <v>105367</v>
       </c>
       <c r="E43" s="7" t="n">
         <v>113475</v>
@@ -4420,16 +5136,16 @@
         </is>
       </c>
       <c r="B44" s="7" t="n">
-        <v>79735</v>
+        <v>79731</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>79858</v>
+        <v>79857</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>82683</v>
+        <v>82682</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>89671</v>
+        <v>89670</v>
       </c>
       <c r="F44" s="7" t="n">
         <v>88866</v>
@@ -4469,13 +5185,13 @@
         </is>
       </c>
       <c r="B46" s="7" t="n">
-        <v>106654.56786</v>
+        <v>106651.184328</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>111205.4184</v>
+        <v>111204.290556</v>
       </c>
       <c r="D46" s="7" t="n">
-        <v>118839.794436</v>
+        <v>118837.538748</v>
       </c>
       <c r="E46" s="7" t="n">
         <v>127982.0979</v>
@@ -4525,13 +5241,13 @@
         </is>
       </c>
       <c r="B48" s="11" t="n">
-        <v>0.1848874319251309</v>
+        <v>0.184893297519088</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>0.1773212981744422</v>
+        <v>0.1773230965831297</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>0.165930017367537</v>
+        <v>0.1659331669308227</v>
       </c>
       <c r="E48" s="11" t="n">
         <v>0.1540769332452082</v>
@@ -4718,16 +5434,16 @@
         </is>
       </c>
       <c r="B63" s="7" t="n">
-        <v>4140</v>
+        <v>4138</v>
       </c>
       <c r="C63" s="7" t="n">
-        <v>59139</v>
+        <v>59160</v>
       </c>
       <c r="D63" s="7" t="n">
         <v>150089</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>458614</v>
+        <v>458587</v>
       </c>
       <c r="F63" s="12" t="n"/>
       <c r="G63" s="12" t="n"/>
@@ -4740,16 +5456,16 @@
         </is>
       </c>
       <c r="B64" s="7" t="n">
-        <v>4549</v>
+        <v>4547</v>
       </c>
       <c r="C64" s="7" t="n">
-        <v>58261</v>
+        <v>58281</v>
       </c>
       <c r="D64" s="7" t="n">
-        <v>150082</v>
+        <v>150081</v>
       </c>
       <c r="E64" s="7" t="n">
-        <v>455835</v>
+        <v>455808</v>
       </c>
       <c r="F64" s="12" t="n"/>
       <c r="G64" s="12" t="n"/>
@@ -4762,16 +5478,16 @@
         </is>
       </c>
       <c r="B65" s="7" t="n">
-        <v>4552</v>
+        <v>4551</v>
       </c>
       <c r="C65" s="7" t="n">
-        <v>59079</v>
+        <v>59099</v>
       </c>
       <c r="D65" s="7" t="n">
         <v>152118</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>466392</v>
+        <v>466363</v>
       </c>
       <c r="F65" s="12" t="n"/>
       <c r="G65" s="12" t="n"/>
@@ -4784,16 +5500,16 @@
         </is>
       </c>
       <c r="B66" s="7" t="n">
-        <v>4741</v>
+        <v>4739</v>
       </c>
       <c r="C66" s="7" t="n">
-        <v>63403</v>
+        <v>63423</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>162056</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>501214</v>
+        <v>501185</v>
       </c>
       <c r="F66" s="12" t="n"/>
       <c r="G66" s="12" t="n"/>
@@ -4806,16 +5522,16 @@
         </is>
       </c>
       <c r="B67" s="7" t="n">
-        <v>5239</v>
+        <v>5237</v>
       </c>
       <c r="C67" s="7" t="n">
-        <v>65083</v>
+        <v>65104</v>
       </c>
       <c r="D67" s="7" t="n">
         <v>165142</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>516916</v>
+        <v>516884</v>
       </c>
       <c r="F67" s="12" t="n"/>
       <c r="G67" s="12" t="n"/>
@@ -4828,16 +5544,16 @@
         </is>
       </c>
       <c r="B68" s="11" t="n">
-        <v>0.2654589371980676</v>
+        <v>0.2655872402126631</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>0.1005089703917887</v>
+        <v>0.100473292765382</v>
       </c>
       <c r="D68" s="11" t="n">
         <v>0.1002938256634396</v>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.1271265159807595</v>
+        <v>0.1271230976892062</v>
       </c>
       <c r="F68" s="12" t="n"/>
       <c r="G68" s="12" t="n"/>
@@ -4855,16 +5571,16 @@
         </is>
       </c>
       <c r="B69" s="11" t="n">
-        <v>0.06062537773196808</v>
+        <v>0.06065226052044004</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>0.02423213297708893</v>
+        <v>0.02422383167818176</v>
       </c>
       <c r="D69" s="11" t="n">
         <v>0.02418207107245318</v>
       </c>
       <c r="E69" s="11" t="n">
-        <v>0.03036990821614882</v>
+        <v>0.03036912700199279</v>
       </c>
       <c r="F69" s="12" t="n"/>
       <c r="G69" s="12" t="n"/>
@@ -4904,13 +5620,13 @@
         <v>2026</v>
       </c>
       <c r="B73" s="10" t="n">
-        <v>2469.37</v>
+        <v>2468.69</v>
       </c>
       <c r="C73" s="11" t="n">
-        <v>0.002793919975309533</v>
+        <v>0.002517776721935983</v>
       </c>
       <c r="D73" s="11" t="n">
-        <v>0.0431</v>
+        <v>0.04389999999999999</v>
       </c>
     </row>
     <row r="74">
@@ -5117,16 +5833,16 @@
         </is>
       </c>
       <c r="B88" s="11" t="n">
-        <v>0.1675892345867532</v>
+        <v>0.1676532365858316</v>
       </c>
       <c r="C88" s="11" t="n">
-        <v>0.1324022003011585</v>
+        <v>0.1323574588350946</v>
       </c>
       <c r="D88" s="11" t="n">
-        <v>0.128294871717239</v>
+        <v>0.1282956485933318</v>
       </c>
       <c r="E88" s="11" t="n">
-        <v>0.1575223875399726</v>
+        <v>0.1575340743105333</v>
       </c>
       <c r="F88" s="11" t="n">
         <v>0.1439230188830762</v>
@@ -5150,16 +5866,16 @@
         </is>
       </c>
       <c r="B89" s="11" t="n">
-        <v>0.1402939492269517</v>
+        <v>0.1403475272102349</v>
       </c>
       <c r="C89" s="11" t="n">
-        <v>0.1312959036292677</v>
+        <v>0.1312668960432539</v>
       </c>
       <c r="D89" s="11" t="n">
-        <v>0.1295604415567115</v>
+        <v>0.1295612260963292</v>
       </c>
       <c r="E89" s="11" t="n">
-        <v>0.1260357078602561</v>
+        <v>0.1260396413128646</v>
       </c>
       <c r="F89" s="11" t="n">
         <v>0.1090536545703669</v>
@@ -5183,16 +5899,16 @@
         </is>
       </c>
       <c r="B90" s="11" t="n">
-        <v>0.1093720175606032</v>
+        <v>0.1094137865189994</v>
       </c>
       <c r="C90" s="11" t="n">
-        <v>0.09160751052518361</v>
+        <v>0.09159191447530106</v>
       </c>
       <c r="D90" s="11" t="n">
-        <v>0.09612275421907074</v>
+        <v>0.09612333628029211</v>
       </c>
       <c r="E90" s="11" t="n">
-        <v>0.0974934080326242</v>
+        <v>0.09749944378343345</v>
       </c>
       <c r="F90" s="11" t="n">
         <v>0.09153364975214603</v>
@@ -5216,16 +5932,16 @@
         </is>
       </c>
       <c r="B91" s="11" t="n">
-        <v>0.09200229051345676</v>
+        <v>0.09203742600725606</v>
       </c>
       <c r="C91" s="11" t="n">
-        <v>0.1102148059371255</v>
+        <v>0.1101929220938806</v>
       </c>
       <c r="D91" s="11" t="n">
-        <v>0.09007950685163767</v>
+        <v>0.09008005231861065</v>
       </c>
       <c r="E91" s="11" t="n">
-        <v>0.07061675278623067</v>
+        <v>0.07061532062257563</v>
       </c>
       <c r="F91" s="11" t="n">
         <v>0.08654896600644772</v>
@@ -5249,16 +5965,16 @@
         </is>
       </c>
       <c r="B92" s="11" t="n">
-        <v>0.03397594960870395</v>
+        <v>0.03398892495703647</v>
       </c>
       <c r="C92" s="11" t="n">
-        <v>0.1437571064195937</v>
+        <v>0.1437238879331531</v>
       </c>
       <c r="D92" s="11" t="n">
-        <v>0.1065198040486124</v>
+        <v>0.1065265044628259</v>
       </c>
       <c r="E92" s="11" t="n">
-        <v>0.07423822393150158</v>
+        <v>0.07424281996962574</v>
       </c>
       <c r="F92" s="11" t="n">
         <v>0.07168567465967132</v>
@@ -5282,16 +5998,16 @@
         </is>
       </c>
       <c r="B93" s="11" t="n">
-        <v>0.05630845581217789</v>
+        <v>0.05632995990070651</v>
       </c>
       <c r="C93" s="11" t="n">
-        <v>0.09185335423004824</v>
+        <v>0.09206807569427378</v>
       </c>
       <c r="D93" s="11" t="n">
-        <v>0.1103528457155314</v>
+        <v>0.1103474585508229</v>
       </c>
       <c r="E93" s="11" t="n">
-        <v>0.09778359001541834</v>
+        <v>0.09778383973224218</v>
       </c>
       <c r="F93" s="11" t="n">
         <v>0.0692937123890178</v>
@@ -5315,16 +6031,16 @@
         </is>
       </c>
       <c r="B94" s="11" t="n">
-        <v>0.01355220461920214</v>
+        <v>0.01355738017949207</v>
       </c>
       <c r="C94" s="11" t="n">
-        <v>0.02564457146369196</v>
+        <v>0.02563590562791841</v>
       </c>
       <c r="D94" s="11" t="n">
-        <v>0.02846623835100489</v>
+        <v>0.02846641072531518</v>
       </c>
       <c r="E94" s="11" t="n">
-        <v>0.06430626193373404</v>
+        <v>0.06430443909186763</v>
       </c>
       <c r="F94" s="11" t="n">
         <v>0.06699836548547758</v>
@@ -5348,16 +6064,16 @@
         </is>
       </c>
       <c r="B95" s="11" t="n">
-        <v>0.005344531399121969</v>
+        <v>0.005346572465151804</v>
       </c>
       <c r="C95" s="11" t="n">
-        <v>0.03838234842199072</v>
+        <v>0.03838473826492996</v>
       </c>
       <c r="D95" s="11" t="n">
-        <v>0.04546362849167086</v>
+        <v>0.04546390379188819</v>
       </c>
       <c r="E95" s="11" t="n">
-        <v>0.06499302595968018</v>
+        <v>0.06499124563490911</v>
       </c>
       <c r="F95" s="11" t="n">
         <v>0.06180957654864814</v>
@@ -5381,16 +6097,16 @@
         </is>
       </c>
       <c r="B96" s="11" t="n">
-        <v>0.03531208245848445</v>
+        <v>0.03532556807332442</v>
       </c>
       <c r="C96" s="11" t="n">
-        <v>0.06550198211487047</v>
+        <v>0.06547984762840993</v>
       </c>
       <c r="D96" s="11" t="n">
-        <v>0.05942728423245309</v>
+        <v>0.0594276440881181</v>
       </c>
       <c r="E96" s="11" t="n">
-        <v>0.06130384568509065</v>
+        <v>0.06130183696566935</v>
       </c>
       <c r="F96" s="11" t="n">
         <v>0.06005544300027939</v>
@@ -5414,16 +6130,16 @@
         </is>
       </c>
       <c r="B97" s="11" t="n">
-        <v>0.01068906279824394</v>
+        <v>0.01069314493030361</v>
       </c>
       <c r="C97" s="11" t="n">
-        <v>0.006038536000737531</v>
+        <v>0.006036495453428361</v>
       </c>
       <c r="D97" s="11" t="n">
-        <v>0.01906832260525726</v>
+        <v>0.01906843807147788</v>
       </c>
       <c r="E97" s="11" t="n">
-        <v>0.02301916942178338</v>
+        <v>0.0230167251903228</v>
       </c>
       <c r="F97" s="11" t="n">
         <v>0.0473268911935302</v>
@@ -5447,16 +6163,16 @@
         </is>
       </c>
       <c r="B98" s="11" t="n">
-        <v>0.007825920977285742</v>
+        <v>0.007828909681115142</v>
       </c>
       <c r="C98" s="11" t="n">
-        <v>0.03606219845733075</v>
+        <v>0.03605001228803146</v>
       </c>
       <c r="D98" s="11" t="n">
-        <v>0.03811847913626373</v>
+        <v>0.03811870995870221</v>
       </c>
       <c r="E98" s="11" t="n">
-        <v>0.03247329842121656</v>
+        <v>0.03245015815897153</v>
       </c>
       <c r="F98" s="11" t="n">
         <v>0.04109248140049621</v>
@@ -5483,13 +6199,13 @@
         <v>0</v>
       </c>
       <c r="C99" s="11" t="n">
-        <v>0.001859193018038782</v>
+        <v>0.001873924797247481</v>
       </c>
       <c r="D99" s="11" t="n">
-        <v>0.02761848821930085</v>
+        <v>0.02761865546014945</v>
       </c>
       <c r="E99" s="11" t="n">
-        <v>0.02183329238543132</v>
+        <v>0.02183464406976407</v>
       </c>
       <c r="F99" s="11" t="n">
         <v>0.03285591679200175</v>
@@ -5513,16 +6229,16 @@
         </is>
       </c>
       <c r="B100" s="11" t="n">
-        <v>0.01546096583317427</v>
+        <v>0.01546687034561772</v>
       </c>
       <c r="C100" s="11" t="n">
-        <v>0.02945514888909376</v>
+        <v>0.02944519537970017</v>
       </c>
       <c r="D100" s="11" t="n">
-        <v>0.03031917792458657</v>
+        <v>0.03031936151917744</v>
       </c>
       <c r="E100" s="11" t="n">
-        <v>0.02663677147395037</v>
+        <v>0.02663842053841764</v>
       </c>
       <c r="F100" s="11" t="n">
         <v>0.02745633069056147</v>
@@ -5546,16 +6262,16 @@
         </is>
       </c>
       <c r="B101" s="11" t="n">
-        <v>0.2744798625691926</v>
+        <v>0.2742027878556426</v>
       </c>
       <c r="C101" s="11" t="n">
-        <v>0.03211333394794259</v>
+        <v>0.03210248218235439</v>
       </c>
       <c r="D101" s="11" t="n">
-        <v>0.0287326741066833</v>
+        <v>0.02873284809436727</v>
       </c>
       <c r="E101" s="11" t="n">
-        <v>0.02107301559051066</v>
+        <v>0.02107432020662236</v>
       </c>
       <c r="F101" s="11" t="n">
         <v>0.02090656164729619</v>
@@ -5579,16 +6295,16 @@
         </is>
       </c>
       <c r="B102" s="11" t="n">
-        <v>0.03340332124451231</v>
+        <v>0.03341607790719878</v>
       </c>
       <c r="C102" s="11" t="n">
-        <v>0.03411081404996773</v>
+        <v>0.03409928729417547</v>
       </c>
       <c r="D102" s="11" t="n">
-        <v>0.02407610374039469</v>
+        <v>0.02407019413595572</v>
       </c>
       <c r="E102" s="11" t="n">
-        <v>0.02037464428525276</v>
+        <v>0.02037590566567031</v>
       </c>
       <c r="F102" s="11" t="n">
         <v>0.02084382439592392</v>
@@ -5612,16 +6328,16 @@
         </is>
       </c>
       <c r="B103" s="11" t="n">
-        <v>0.002672265699560985</v>
+        <v>0.002673286232575902</v>
       </c>
       <c r="C103" s="11" t="n">
-        <v>0.01090931440336806</v>
+        <v>0.01090562791840747</v>
       </c>
       <c r="D103" s="11" t="n">
-        <v>0.01293424486657018</v>
+        <v>0.01293432318852866</v>
       </c>
       <c r="E103" s="11" t="n">
-        <v>0.01705883149519169</v>
+        <v>0.0170598875958869</v>
       </c>
       <c r="F103" s="11" t="n">
         <v>0.01906250470529385</v>
@@ -5645,16 +6361,16 @@
         </is>
       </c>
       <c r="B104" s="11" t="n">
-        <v>0.0005726283641916397</v>
+        <v>0.0005728470498376934</v>
       </c>
       <c r="C104" s="11" t="n">
-        <v>0.01676346762545712</v>
+        <v>0.01675780289997542</v>
       </c>
       <c r="D104" s="11" t="n">
-        <v>0.01896538151783606</v>
+        <v>0.01896549636070775</v>
       </c>
       <c r="E104" s="11" t="n">
-        <v>0.01917522542303697</v>
+        <v>0.01917447788192731</v>
       </c>
       <c r="F104" s="11" t="n">
         <v>0.01809509628913341</v>
@@ -5678,16 +6394,16 @@
         </is>
       </c>
       <c r="B105" s="11" t="n">
-        <v>0.001145256728383279</v>
+        <v>0.001145694099675387</v>
       </c>
       <c r="C105" s="11" t="n">
-        <v>0.0007221658830398574</v>
+        <v>0.0007219218481199312</v>
       </c>
       <c r="D105" s="11" t="n">
-        <v>0.003772488086082971</v>
+        <v>0.003772510929987526</v>
       </c>
       <c r="E105" s="11" t="n">
-        <v>0.002512975970997278</v>
+        <v>0.002513131547636321</v>
       </c>
       <c r="F105" s="11" t="n">
         <v>0.006769767671410718</v>
@@ -5714,13 +6430,13 @@
         <v>0</v>
       </c>
       <c r="C106" s="11" t="n">
-        <v>0.0006299744937156203</v>
+        <v>0.0006297616121897272</v>
       </c>
       <c r="D106" s="11" t="n">
-        <v>0.001725777053826078</v>
+        <v>0.001725787504087392</v>
       </c>
       <c r="E106" s="11" t="n">
-        <v>0.001151055198416767</v>
+        <v>0.001151126459463904</v>
       </c>
       <c r="F106" s="11" t="n">
         <v>0.003239751660864168</v>
@@ -5747,13 +6463,13 @@
         <v>0</v>
       </c>
       <c r="C107" s="11" t="n">
-        <v>0.0006760701883777388</v>
+        <v>0.0006758417301548292</v>
       </c>
       <c r="D107" s="11" t="n">
-        <v>0.0003814875592668172</v>
+        <v>0.0003814898693245813</v>
       </c>
       <c r="E107" s="11" t="n">
-        <v>0.0003985165897039564</v>
+        <v>0.0003985412615959063</v>
       </c>
       <c r="F107" s="11" t="n">
         <v>0.00144881225835702</v>
@@ -5781,7 +6497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L58"/>
+  <dimension ref="A1:L59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -5925,7 +6641,7 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D11" s="7" t="n">
         <v>558</v>
@@ -5961,7 +6677,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>3355</v>
@@ -5979,10 +6695,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>38442</v>
+        <v>39029</v>
       </c>
     </row>
     <row r="15">
@@ -5997,10 +6713,10 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>15187</v>
+        <v>16643</v>
       </c>
     </row>
     <row r="16"/>
@@ -6257,7 +6973,7 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>539 S WILLIAMS</t>
+          <t>Williams Place</t>
         </is>
       </c>
       <c r="B28" s="10" t="n">
@@ -6377,7 +7093,7 @@
         </is>
       </c>
       <c r="B30" s="10" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
@@ -6603,37 +7319,41 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>La Jolla Villas</t>
+          <t>The Bungalows on Ash</t>
         </is>
       </c>
       <c r="B34" s="10" t="n">
-        <v>1.59</v>
+        <v>1.34</v>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Entitlement</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="n">
-        <v>15</v>
+          <t>Permitted</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>multifamily</t>
+          <t>other_mf</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1381 N GILBERT RD</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H34" s="10" t="n">
-        <v>1.07</v>
+          <t>GILBERT</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
@@ -6642,54 +7362,54 @@
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2020-06-25</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>Entitlement</t>
+          <t>County permits</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>1424 E DANA AVE</t>
+          <t>La Jolla Villas</t>
         </is>
       </c>
       <c r="B35" s="10" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Permitted</t>
+          <t>Entitlement</t>
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>apartment_rental</t>
+          <t>multifamily</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>1424 E DANA AVE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Mesa</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H35" s="10" t="n">
-        <v>0.076</v>
+        <v>1.07</v>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
@@ -6698,54 +7418,54 @@
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>County permits</t>
+          <t>Entitlement</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Dana Park Village Square</t>
+          <t>1424 E DANA AVE</t>
         </is>
       </c>
       <c r="B36" s="10" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Entitlement</t>
+          <t>Permitted</t>
         </is>
       </c>
       <c r="D36" s="7" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>multifamily</t>
+          <t>apartment_rental</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1424 E DANA AVE</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mesa</t>
         </is>
       </c>
       <c r="H36" s="10" t="n">
-        <v>4.25</v>
+        <v>0.076</v>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
@@ -6754,58 +7474,54 @@
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>Entitlement</t>
+          <t>County permits</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>214 N GILBERT RD 111</t>
+          <t>Dana Park Village Square</t>
         </is>
       </c>
       <c r="B37" s="10" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Permitted</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Entitlement</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>36</v>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>apartment_rental</t>
+          <t>multifamily</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>214 N GILBERT RD 111</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Mesa</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H37" s="10" t="n">
+        <v>4.25</v>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
@@ -6814,17 +7530,17 @@
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>2023-02-23</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>2023-03-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>County permits</t>
+          <t>Entitlement</t>
         </is>
       </c>
     </row>
@@ -6887,37 +7603,41 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Tangerine</t>
+          <t>214 N GILBERT RD 111</t>
         </is>
       </c>
       <c r="B39" s="10" t="n">
-        <v>2.09</v>
+        <v>1.8</v>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Entitlement</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="n">
-        <v>29</v>
+          <t>Permitted</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>multifamily</t>
+          <t>apartment_rental</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>214 N GILBERT RD 111</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H39" s="10" t="n">
-        <v>2.06</v>
+          <t>Mesa</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
@@ -6926,58 +7646,54 @@
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2023-02-23</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2023-03-01</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>Entitlement</t>
+          <t>County permits</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>3020 E MAIN ST</t>
+          <t>Tangerine</t>
         </is>
       </c>
       <c r="B40" s="10" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Permitted</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Entitlement</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>29</v>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>apartment_rental</t>
+          <t>multifamily</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>3020 E MAIN ST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>Mesa</t>
-        </is>
-      </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H40" s="10" t="n">
+        <v>2.06</v>
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
@@ -6986,32 +7702,32 @@
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>2023-07-27</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>County permits</t>
+          <t>Entitlement</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>La Mesa Village Apartments</t>
+          <t>3020 E MAIN ST</t>
         </is>
       </c>
       <c r="B41" s="10" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Entitlement</t>
+          <t>Permitted</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -7021,17 +7737,17 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>multifamily</t>
+          <t>apartment_rental</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3020 E MAIN ST</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>MESA</t>
+          <t>Mesa</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
@@ -7046,32 +7762,32 @@
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-07-27</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>NOI radar (Arizona DEQ)</t>
+          <t>County permits</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>505 S LESUEUR C</t>
+          <t>La Mesa Village Apartments</t>
         </is>
       </c>
       <c r="B42" s="10" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Permitted</t>
+          <t>Entitlement</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -7081,17 +7797,17 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>apartment_rental</t>
+          <t>multifamily</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>505 S LESUEUR C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>Mesa</t>
+          <t>MESA</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
@@ -7106,54 +7822,58 @@
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>2020-07-23</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>County permits</t>
+          <t>NOI radar (Arizona DEQ)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>Pioneer Place</t>
+          <t>505 S LESUEUR C</t>
         </is>
       </c>
       <c r="B43" s="10" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Entitlement</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="n">
-        <v>9</v>
+          <t>Permitted</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>apartment_rental</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>505 S LESUEUR C</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H43" s="10" t="n">
-        <v>0.83</v>
+          <t>Mesa</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
@@ -7162,28 +7882,28 @@
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2020-07-01</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2020-07-23</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>Entitlement</t>
+          <t>County permits</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>PS16-006 A New Leaf Apartment Bldg</t>
+          <t>Pioneer Place</t>
         </is>
       </c>
       <c r="B44" s="10" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
@@ -7191,11 +7911,11 @@
         </is>
       </c>
       <c r="D44" s="7" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>multifamily</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
@@ -7209,7 +7929,7 @@
         </is>
       </c>
       <c r="H44" s="10" t="n">
-        <v>1.74</v>
+        <v>0.83</v>
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
@@ -7235,39 +7955,37 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>3426 E UNIVERSITY DR</t>
+          <t>PS16-006 A New Leaf Apartment Bldg</t>
         </is>
       </c>
       <c r="B45" s="10" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Permitted</t>
+          <t>Entitlement</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>apartment_rental</t>
+          <t>multifamily</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>3426 E UNIVERSITY DR</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Mesa</t>
-        </is>
-      </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H45" s="10" t="n">
+        <v>1.74</v>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
@@ -7276,38 +7994,36 @@
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>2021-02-15</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>County permits</t>
+          <t>Entitlement</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>455 E MAIN ST</t>
+          <t>3426 E UNIVERSITY DR</t>
         </is>
       </c>
       <c r="B46" s="10" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
           <t>Permitted</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="D46" s="7" t="n">
+        <v>36</v>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
@@ -7316,7 +8032,7 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>455 E MAIN ST</t>
+          <t>3426 E UNIVERSITY DR</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
@@ -7336,12 +8052,12 @@
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>2019-03-07</t>
+          <t>2021-02-15</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>2020-12-08</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="L46" s="5" t="inlineStr">
@@ -7353,37 +8069,41 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Van Damme Residence</t>
+          <t>455 E MAIN ST</t>
         </is>
       </c>
       <c r="B47" s="10" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Entitlement</t>
-        </is>
-      </c>
-      <c r="D47" s="7" t="n">
-        <v>2</v>
+          <t>Permitted</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>multifamily</t>
+          <t>apartment_rental</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>455 E MAIN ST</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H47" s="10" t="n">
-        <v>0.16</v>
+          <t>Mesa</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
@@ -7392,36 +8112,38 @@
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2019-03-07</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2020-12-08</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>Entitlement</t>
+          <t>County permits</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>LEGACY SQUARE</t>
+          <t>ASPIRE HERITAGE</t>
         </is>
       </c>
       <c r="B48" s="10" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Permitted</t>
-        </is>
-      </c>
-      <c r="D48" s="7" t="n">
-        <v>110</v>
+          <t>Entitlement</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
@@ -7430,12 +8152,12 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>140 S POMEROY</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>MESA</t>
+          <t>GILBERT</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
@@ -7445,33 +8167,33 @@
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>Willow Bridge Property Company</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2019-04-24</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>County permits, NOI radar (Arizona DEQ)</t>
+          <t>NOI radar (Arizona DEQ)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Cadillac Aparments</t>
+          <t>Van Damme Residence</t>
         </is>
       </c>
       <c r="B49" s="10" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
@@ -7479,7 +8201,7 @@
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
@@ -7497,7 +8219,7 @@
         </is>
       </c>
       <c r="H49" s="10" t="n">
-        <v>0.85</v>
+        <v>0.16</v>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
@@ -7523,35 +8245,33 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Clare House Social</t>
+          <t>LEGACY SQUARE</t>
         </is>
       </c>
       <c r="B50" s="10" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Entitlement</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Permitted</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>110</v>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>multifamily</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>140 S POMEROY</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MESA</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
@@ -7561,43 +8281,41 @@
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Willow Bridge Property Company</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>Entitlement</t>
+          <t>County permits, NOI radar (Arizona DEQ)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>The Lumberyard</t>
+          <t>Cadillac Aparments</t>
         </is>
       </c>
       <c r="B51" s="10" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
           <t>Entitlement</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="D51" s="7" t="n">
+        <v>7</v>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
@@ -7614,10 +8332,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="H51" s="10" t="n">
+        <v>0.85</v>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
@@ -7626,12 +8342,12 @@
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
@@ -7643,11 +8359,11 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>The Brundrett Building</t>
+          <t>Clare House Social</t>
         </is>
       </c>
       <c r="B52" s="10" t="n">
-        <v>2.72</v>
+        <v>2.65</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
@@ -7686,7 +8402,7 @@
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
@@ -7703,15 +8419,15 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>233 E MAIN ST</t>
+          <t>The Brundrett Building</t>
         </is>
       </c>
       <c r="B53" s="10" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Permitted</t>
+          <t>Entitlement</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -7721,17 +8437,17 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>apartment_rental</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>233 E MAIN ST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Mesa</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -7746,54 +8462,58 @@
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>2020-01-27</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>2022-02-16</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>County permits</t>
+          <t>Entitlement</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>NEC Neely St and Aviary Way</t>
+          <t>233 E MAIN ST</t>
         </is>
       </c>
       <c r="B54" s="10" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Entitlement</t>
-        </is>
-      </c>
-      <c r="D54" s="7" t="n">
-        <v>99</v>
+          <t>Permitted</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>multifamily</t>
+          <t>apartment_rental</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>233 E MAIN ST</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H54" s="10" t="n">
-        <v>11.75</v>
+          <t>Mesa</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
@@ -7802,28 +8522,28 @@
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2020-01-27</t>
         </is>
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
-          <t>Entitlement</t>
+          <t>County permits</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>Mesa Main Street Apartments</t>
+          <t>NEC Neely St and Aviary Way</t>
         </is>
       </c>
       <c r="B55" s="10" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
@@ -7831,7 +8551,7 @@
         </is>
       </c>
       <c r="D55" s="7" t="n">
-        <v>36</v>
+        <v>99</v>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
@@ -7849,7 +8569,7 @@
         </is>
       </c>
       <c r="H55" s="10" t="n">
-        <v>4.33</v>
+        <v>11.75</v>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
@@ -7875,39 +8595,37 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>145 E MAIN ST 1</t>
+          <t>Mesa Main Street Apartments</t>
         </is>
       </c>
       <c r="B56" s="10" t="n">
-        <v>2.89</v>
+        <v>2.81</v>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Permitted</t>
+          <t>Entitlement</t>
         </is>
       </c>
       <c r="D56" s="7" t="n">
-        <v>335</v>
+        <v>36</v>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>apartment_rental</t>
+          <t>multifamily</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>145 E MAIN ST 1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>Mesa</t>
-        </is>
-      </c>
-      <c r="H56" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H56" s="10" t="n">
+        <v>4.33</v>
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
@@ -7916,54 +8634,56 @@
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="K56" s="5" t="inlineStr">
         <is>
-          <t>2021-12-06</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="L56" s="5" t="inlineStr">
         <is>
-          <t>County permits</t>
+          <t>Entitlement</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>Fiesta Rose Garden</t>
+          <t>145 E MAIN ST 1</t>
         </is>
       </c>
       <c r="B57" s="10" t="n">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Entitlement</t>
+          <t>Permitted</t>
         </is>
       </c>
       <c r="D57" s="7" t="n">
-        <v>12</v>
+        <v>335</v>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>multifamily</t>
+          <t>apartment_rental</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>145 E MAIN ST 1</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H57" s="10" t="n">
-        <v>1.03</v>
+          <t>Mesa</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
@@ -7972,71 +8692,127 @@
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2021-04-01</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2021-12-06</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>Entitlement</t>
+          <t>County permits</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
+          <t>Fiesta Rose Garden</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>Entitlement</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>multifamily</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H58" s="10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="L58" s="5" t="inlineStr">
+        <is>
+          <t>Entitlement</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
           <t>NWC Gilbert Rd and Elliot Rd</t>
         </is>
       </c>
-      <c r="B58" s="10" t="n">
+      <c r="B59" s="10" t="n">
         <v>2.99</v>
       </c>
-      <c r="C58" s="5" t="inlineStr">
+      <c r="C59" s="5" t="inlineStr">
         <is>
           <t>Entitlement</t>
         </is>
       </c>
-      <c r="D58" s="7" t="n">
+      <c r="D59" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="E58" s="5" t="inlineStr">
+      <c r="E59" s="5" t="inlineStr">
         <is>
           <t>mixed</t>
         </is>
       </c>
-      <c r="F58" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G58" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H58" s="10" t="n">
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H59" s="10" t="n">
         <v>2.19</v>
       </c>
-      <c r="I58" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J58" s="5" t="inlineStr">
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="K58" s="5" t="inlineStr">
+      <c r="K59" s="5" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="L58" s="5" t="inlineStr">
+      <c r="L59" s="5" t="inlineStr">
         <is>
           <t>Entitlement</t>
         </is>
@@ -8292,7 +9068,7 @@
       </c>
       <c r="C16" s="22" t="inlineStr">
         <is>
-          <t>This subject was built 1981. Two comp sets were selected by identical criteria — same candidate pool, same product test, same tracker exclusions, same radius, same closest-20 cap, same rent rules, same mix weighting — differing only in whether the +/-10-year vintage test was applied. Set A, vintage test ON: 10 communities, vintages 1981 to 1987; this subject's rent reads 12.1% above it. Set B, vintage test OFF: 3 more communities join and none drops out — fewer than 20 qualify either way, so the cap never binds (vintages 1981 to 2018); the same rent reads 8.0% above it. Both figures are weighted by this property's own unit mix and computed over the same bed counts (95% of its units), so the two sets differ by 4.1 points. Every community that joins was built after 1987, set A's newest, so set B reaches newer product than the vintage test allowed. Both sets are listed on the Rent Comps section — this is a measurement of these two sets on this date, not an estimate of what vintage is worth in this market.</t>
+          <t>This subject was built 1981. Two comp sets were selected by identical criteria — same candidate pool, same product test, same tracker exclusions, same radius, same closest-20 cap, same rent rules, same mix weighting — differing only in whether the +/-10-year vintage test was applied. Set A, vintage test ON: 13 communities, vintages 1981 to 1987; this subject's rent reads 4.7% above it. Set B, vintage test OFF: 4 more communities join and none drops out — fewer than 20 qualify either way, so the cap never binds (vintages 1981 to 2018); the same rent reads 0.8% above it. Both figures are weighted by this property's own unit mix and computed over the same bed counts (95% of its units), so the two sets differ by 3.9 points. Every community that joins was built after 1987, set A's newest, so set B reaches newer product than the vintage test allowed. Both sets are listed on the Rent Comps section — this is a measurement of these two sets on this date, not an estimate of what vintage is worth in this market.</t>
         </is>
       </c>
     </row>
@@ -8394,7 +9170,7 @@
       </c>
       <c r="C22" s="22" t="inlineStr">
         <is>
-          <t>Supply: the 32 development(s) within 3 mi are listed by name, one row each, at the furthest stage the pipeline shows; beyond that radius the rings are counts only.</t>
+          <t>Supply: the 33 development(s) within 3 mi are listed by name, one row each, at the furthest stage the pipeline shows; beyond that radius the rings are counts only.</t>
         </is>
       </c>
     </row>
@@ -8411,7 +9187,7 @@
       </c>
       <c r="C23" s="22" t="inlineStr">
         <is>
-          <t>Supply: 214 row(s) were the same development on more than one lifecycle layer and were counted once, at the furthest stage the pipeline shows.</t>
+          <t>Supply: 215 row(s) were the same development on more than one lifecycle layer and were counted once, at the furthest stage the pipeline shows.</t>
         </is>
       </c>
     </row>
@@ -8428,7 +9204,7 @@
       </c>
       <c r="C24" s="22" t="inlineStr">
         <is>
-          <t>Supply: 145 project(s) without a unit count are counted as projects and add zero units — the unit figure is a floor, not a total.</t>
+          <t>Supply: 141 project(s) without a unit count are counted as projects and add zero units — the unit figure is a floor, not a total.</t>
         </is>
       </c>
     </row>
@@ -8513,7 +9289,7 @@
       </c>
       <c r="C29" s="22" t="inlineStr">
         <is>
-          <t>Rent comps: 344 of 351 communities in the radius carry a year built (parsed from the tracker's vendor note); those are vintage-tested against the subject, the rest are matched on distance and product only and say so.</t>
+          <t>Rent comps: 354 of 357 communities in the radius carry a year built (297 from the public property record, the rest from the community registry); those are vintage-tested against the subject, the rest are matched on distance and product only and say so.</t>
         </is>
       </c>
     </row>
@@ -8530,7 +9306,7 @@
       </c>
       <c r="C30" s="22" t="inlineStr">
         <is>
-          <t>Rent comps: the in-radius population (351 communities) was read from the service's audit rows with the registry's product, exclusion flag and year built; the 331 beyond its 20 preselected are tiered on those but carry no quoted rent, so they are carried in the interchange file without one.</t>
+          <t>Rent comps: 297 of 357 communities in the radius carry a public-record unit count (Maricopa County, AZ property record), shown with its source and as-of. A community's licensed registry count is never published; where no public record covers it, the count reads MISSING and says so.</t>
         </is>
       </c>
     </row>
@@ -8547,7 +9323,7 @@
       </c>
       <c r="C31" s="22" t="inlineStr">
         <is>
-          <t>Rent comps: the service did not provide the lowest-five rent measure; rows marked 'group floor' quote the single lowest listing, which reads BELOW the lowest-five average.</t>
+          <t>Rent comps: 1 quoted community is marked STALE by the tracker (snapshot older than its freshness threshold); their rows say so.</t>
         </is>
       </c>
     </row>
@@ -8564,7 +9340,7 @@
       </c>
       <c r="C32" s="22" t="inlineStr">
         <is>
-          <t>Rent comps: 1 community name(s) would fail the publishing check and are withheld; their rows stay, by distance and units.</t>
+          <t>Rent comps: 1 community name(s) would fail the publishing check and are withheld; their rows stay, by distance (a licensed unit count is never published).</t>
         </is>
       </c>
     </row>
@@ -8581,7 +9357,7 @@
       </c>
       <c r="C33" s="22" t="inlineStr">
         <is>
-          <t>Rent comps: 13 unit group(s) the tracker flagged for review were not quoted.</t>
+          <t>Rent comps: 12 unit group(s) the tracker flagged for review were not quoted.</t>
         </is>
       </c>
     </row>
@@ -8783,7 +9559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -8833,7 +9609,7 @@
         </is>
       </c>
       <c r="B5" s="23" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6">
@@ -8959,7 +9735,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>340 entries</t>
+          <t>343 entries</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -9017,7 +9793,7 @@
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="22" t="inlineStr">
         <is>
-          <t>Unit counts come from a licensed data export; the internal pipeline carries them.</t>
+          <t>A community's own unit count comes from a licensed data export, so the public demo holds it back; where a public record states a count (a county property record, a Florida DBPR apartment licence, a City of Austin permit), that count is shown with its source and as-of.</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9805,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>19 entries</t>
+          <t>26 entries</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -9094,22 +9870,22 @@
     <row r="15">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>demand.rings</t>
+          <t>comps.rows[].units</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>5 entries</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Public demographic data (the operator's ring engine), via the market-report service</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>POST /report (format json)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -9120,24 +9896,24 @@
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="22" t="inlineStr">
         <is>
-          <t>Ring demographics.</t>
+          <t>A community's own unit count comes from a licensed data export, so the public demo holds it back; where a public record states a count (a county property record, a Florida DBPR apartment licence, a City of Austin permit), that count is shown with its source and as-of.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>demand.zip_home</t>
+          <t>demand.rings</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5 entries</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Zillow ZHVI home values (vendored static table, undated), via the market-report service</t>
+          <t>Public demographic data (the operator's ring engine), via the market-report service</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -9153,29 +9929,29 @@
       <c r="F16" s="12" t="n"/>
       <c r="G16" s="22" t="inlineStr">
         <is>
-          <t>ZIP and metro home values from the vendored Zillow ZHVI table; static, undated.</t>
+          <t>Ring demographics.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>om_comps.rent</t>
+          <t>demand.zip_home</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>0 entries</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
+          <t>Zillow ZHVI home values (vendored static table, undated), via the market-report service</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>p.20</t>
+          <t>POST /report (format json)</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -9186,29 +9962,29 @@
       <c r="F17" s="12" t="n"/>
       <c r="G17" s="22" t="inlineStr">
         <is>
-          <t>4 rent comparable(s) the memorandum states; every figure verified inside its own quote.</t>
+          <t>ZIP and metro home values from the vendored Zillow ZHVI table; static, undated.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>pricing.price_per_unit</t>
+          <t>om_comps.rent</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>215,000</t>
+          <t>0 entries</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Illustrative price</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>p.20</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -9219,24 +9995,24 @@
       <c r="F18" s="12" t="n"/>
       <c r="G18" s="22" t="inlineStr">
         <is>
-          <t>Per-unit price chosen for the sample, inside the sale-price band; every cap rate and pricing ladder is computed from it.</t>
+          <t>4 rent comparable(s) the memorandum states; every figure verified inside its own quote.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="24" t="inlineStr">
         <is>
-          <t>pricing.unit_count</t>
+          <t>pricing.price_per_unit</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>215,000</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Sample Property RR 8.4.26.xlsx</t>
+          <t>Illustrative price</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -9246,34 +10022,30 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>summary.unit_count</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="n"/>
       <c r="G19" s="22" t="inlineStr">
         <is>
-          <t>The same count the summary carries, counted from the rows of the uploaded rent roll.</t>
+          <t>Per-unit price chosen for the sample, inside the sale-price band; every cap rate and pricing ladder is computed from it.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>summary.address_provenance</t>
+          <t>pricing.unit_count</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for t…</t>
+          <t>334</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Illustrative address</t>
+          <t>Sample Property RR 8.4.26.xlsx</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -9283,30 +10055,34 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F20" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>summary.unit_count</t>
+        </is>
+      </c>
       <c r="G20" s="22" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
+          <t>The same count the summary carries, counted from the rows of the uploaded rent roll.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>summary.assessed_value_basis</t>
+          <t>summary.address_provenance</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for t…</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Illustrative address</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -9322,29 +10098,29 @@
       <c r="F21" s="12" t="n"/>
       <c r="G21" s="22" t="inlineStr">
         <is>
-          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-10-06.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="24" t="inlineStr">
         <is>
-          <t>summary.assessment_ratio</t>
+          <t>summary.assessed_value_basis</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Vendored county rate table</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>property_tax_table.STATE_RULES['AZ']</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -9355,29 +10131,29 @@
       <c r="F22" s="12" t="n"/>
       <c r="G22" s="22" t="inlineStr">
         <is>
-          <t>10% — legal class 4.2, residential rental. A.R.S. sec. 42-15003 (class four assessed at 10%); A.R.S. sec. 42-12004 (class four includes residential rental property).</t>
+          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="24" t="inlineStr">
         <is>
-          <t>summary.city</t>
+          <t>summary.assessment_ratio</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Mesa</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Illustrative address</t>
+          <t>Vendored county rate table</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>property_tax_table.STATE_RULES['AZ']</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -9388,24 +10164,24 @@
       <c r="F23" s="12" t="n"/>
       <c r="G23" s="22" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
+          <t>10% — legal class 4.2, residential rental. A.R.S. sec. 42-15003 (class four assessed at 10%); A.R.S. sec. 42-12004 (class four includes residential rental property).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="24" t="inlineStr">
         <is>
-          <t>summary.construction_status</t>
+          <t>summary.city</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>Mesa</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Not stated in the uploaded documents</t>
+          <t>Illustrative address</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -9421,24 +10197,24 @@
       <c r="F24" s="12" t="n"/>
       <c r="G24" s="22" t="inlineStr">
         <is>
-          <t>No uploaded document stated this, so the value reads MISSING. Nothing was assumed to fill it.</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-10-06.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="24" t="inlineStr">
         <is>
-          <t>summary.county</t>
+          <t>summary.construction_status</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Maricopa</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Illustrative address</t>
+          <t>Not stated in the uploaded documents</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -9454,24 +10230,24 @@
       <c r="F25" s="12" t="n"/>
       <c r="G25" s="22" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
+          <t>No uploaded document stated this, so the value reads MISSING. Nothing was assumed to fill it.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
         <is>
-          <t>summary.deal_name</t>
+          <t>summary.county</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Sample Mesa Apt</t>
+          <t>Maricopa</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Illustrative name</t>
+          <t>Illustrative address</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -9487,24 +10263,24 @@
       <c r="F26" s="12" t="n"/>
       <c r="G26" s="22" t="inlineStr">
         <is>
-          <t>An illustrative name for the public sample. The real asset's name is withheld; the memorandum's own name for it does not appear anywhere in this set.</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-10-06.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="24" t="inlineStr">
         <is>
-          <t>summary.deal_status</t>
+          <t>summary.deal_name</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>Sample Mesa Apt</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Not stated in the uploaded documents</t>
+          <t>Illustrative name</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -9520,14 +10296,14 @@
       <c r="F27" s="12" t="n"/>
       <c r="G27" s="22" t="inlineStr">
         <is>
-          <t>No uploaded document stated this, so the value reads MISSING. Nothing was assumed to fill it.</t>
+          <t>An illustrative name for the public sample. The real asset's name is withheld; the memorandum's own name for it does not appear anywhere in this set.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="24" t="inlineStr">
         <is>
-          <t>summary.delivery_date</t>
+          <t>summary.deal_status</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -9560,7 +10336,7 @@
     <row r="29">
       <c r="A29" s="24" t="inlineStr">
         <is>
-          <t>summary.fair_market_value</t>
+          <t>summary.delivery_date</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -9570,7 +10346,7 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Not stated in the uploaded documents</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -9586,24 +10362,24 @@
       <c r="F29" s="12" t="n"/>
       <c r="G29" s="22" t="inlineStr">
         <is>
-          <t>The internal pipeline pulls a market value by web lookup; the demo does not reach the web.</t>
+          <t>No uploaded document stated this, so the value reads MISSING. Nothing was assumed to fill it.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="24" t="inlineStr">
         <is>
-          <t>summary.in_place_rent_avg</t>
+          <t>summary.fair_market_value</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>1,456.99</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Sample Property RR 8.4.26.xlsx</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -9613,34 +10389,30 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>rent_roll.units</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="n"/>
       <c r="G30" s="22" t="inlineStr">
         <is>
-          <t>Unit-weighted across the uploaded roll.</t>
+          <t>The internal pipeline pulls a market value by web lookup; the demo does not reach the web.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="24" t="inlineStr">
         <is>
-          <t>summary.listing_brokerage</t>
+          <t>summary.in_place_rent_avg</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Desert Ridge Capital Advisors</t>
+          <t>1,456.99</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Illustrative name</t>
+          <t>Sample Property RR 8.4.26.xlsx</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -9650,30 +10422,34 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F31" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>rent_roll.units</t>
+        </is>
+      </c>
       <c r="G31" s="22" t="inlineStr">
         <is>
-          <t>An illustrative name. The real party is withheld from the public sample.</t>
+          <t>Unit-weighted across the uploaded roll.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="24" t="inlineStr">
         <is>
-          <t>summary.market_rent_for_model</t>
+          <t>summary.listing_brokerage</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>1,344.6</t>
+          <t>Desert Ridge Capital Advisors</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Sample Property RR 8.4.26.xlsx</t>
+          <t>Illustrative name</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -9683,34 +10459,30 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>rent_roll.units</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="n"/>
       <c r="G32" s="22" t="inlineStr">
         <is>
-          <t>Unit-weighted across the uploaded roll.</t>
+          <t>An illustrative name. The real party is withheld from the public sample.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="24" t="inlineStr">
         <is>
-          <t>summary.msa</t>
+          <t>summary.market_rent_for_model</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Phoenix MSA</t>
+          <t>1,344.6</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Illustrative address</t>
+          <t>Sample Property RR 8.4.26.xlsx</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -9720,30 +10492,34 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F33" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>rent_roll.units</t>
+        </is>
+      </c>
       <c r="G33" s="22" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
+          <t>Unit-weighted across the uploaded roll.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="24" t="inlineStr">
         <is>
-          <t>summary.pricing_guidance</t>
+          <t>summary.msa</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>$215,000 per unit (illustrative)</t>
+          <t>Phoenix MSA</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Illustrative price</t>
+          <t>Illustrative address</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -9759,29 +10535,29 @@
       <c r="F34" s="12" t="n"/>
       <c r="G34" s="22" t="inlineStr">
         <is>
-          <t>Every price and cap rate below is illustrative. The per-unit price is a round number chosen for the sample inside the band a real per-unit sale price occupies; it is not a quote, an offer, or a broker's guidance.</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-10-06.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="24" t="inlineStr">
         <is>
-          <t>summary.product_detail</t>
+          <t>summary.pricing_guidance</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Diversified mix of one-, two-, and three-bedroom residences averaging 856 square feet o…</t>
+          <t>$215,000 per unit (illustrative)</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
+          <t>Illustrative price</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>p.3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -9791,6 +10567,39 @@
       </c>
       <c r="F35" s="12" t="n"/>
       <c r="G35" s="22" t="inlineStr">
+        <is>
+          <t>Every price and cap rate below is illustrative. The per-unit price is a round number chosen for the sample inside the band a real per-unit sale price occupies; it is not a quote, an offer, or a broker's guidance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>summary.product_detail</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Diversified mix of one-, two-, and three-bedroom residences averaging 856 square feet o…</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Sample Property Offering Memorandum.pdf</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>p.3</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="n"/>
+      <c r="G36" s="22" t="inlineStr">
         <is>
           <t>the property offers a diversified mix of 
 one-, two-, and three-bedroom residences averaging 856 square 
@@ -9798,58 +10607,25 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="24" t="inlineStr">
-        <is>
-          <t>summary.product_type</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>Garden-style multifamily</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>p.3</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F36" s="12" t="n"/>
-      <c r="G36" s="22" t="inlineStr">
-        <is>
-          <t>Stated in the memorandum; withheld from the public sample because it identifies the real asset.</t>
-        </is>
-      </c>
-    </row>
     <row r="37">
       <c r="A37" s="24" t="inlineStr">
         <is>
-          <t>summary.school_elementary_name</t>
+          <t>summary.product_type</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Porter Elementary School</t>
+          <t>Garden-style multifamily</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Internal underwriting agent — attendance-zone school lookup</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>2151 E Southern Ave, Mesa, AZ 85204 on 2026-09-14</t>
+          <t>p.3</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -9860,19 +10636,19 @@
       <c r="F37" s="12" t="n"/>
       <c r="G37" s="22" t="inlineStr">
         <is>
-          <t>Looked up for the illustrative address by the internal underwriting agent; the public demo does not run this on an uploaded deal.</t>
+          <t>Stated in the memorandum; withheld from the public sample because it identifies the real asset.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="24" t="inlineStr">
         <is>
-          <t>summary.school_high_name</t>
+          <t>summary.school_elementary_name</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Mesa High School</t>
+          <t>Porter Elementary School</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -9900,12 +10676,12 @@
     <row r="39">
       <c r="A39" s="24" t="inlineStr">
         <is>
-          <t>summary.school_middle_name</t>
+          <t>summary.school_high_name</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Taylor Junior High School</t>
+          <t>Mesa High School</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -9933,22 +10709,22 @@
     <row r="40">
       <c r="A40" s="24" t="inlineStr">
         <is>
-          <t>summary.seller_entity</t>
+          <t>summary.school_middle_name</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Sonoran Residential Holdings LLC</t>
+          <t>Taylor Junior High School</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Illustrative name</t>
+          <t>Internal underwriting agent — attendance-zone school lookup</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2151 E Southern Ave, Mesa, AZ 85204 on 2026-09-14</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -9959,24 +10735,24 @@
       <c r="F40" s="12" t="n"/>
       <c r="G40" s="22" t="inlineStr">
         <is>
-          <t>An illustrative name. The real party is withheld from the public sample.</t>
+          <t>Looked up for the illustrative address by the internal underwriting agent; the public demo does not run this on an uploaded deal.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="24" t="inlineStr">
         <is>
-          <t>summary.state</t>
+          <t>summary.seller_entity</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Sonoran Residential Holdings LLC</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Illustrative address</t>
+          <t>Illustrative name</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -9992,19 +10768,19 @@
       <c r="F41" s="12" t="n"/>
       <c r="G41" s="22" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
+          <t>An illustrative name. The real party is withheld from the public sample.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="24" t="inlineStr">
         <is>
-          <t>summary.street_address</t>
+          <t>summary.state</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>2151 E Southern Ave</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -10025,29 +10801,29 @@
       <c r="F42" s="12" t="n"/>
       <c r="G42" s="22" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-10-06.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="24" t="inlineStr">
         <is>
-          <t>summary.structure</t>
+          <t>summary.street_address</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>1 &amp; 2 stories</t>
+          <t>2151 E Southern Ave</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
+          <t>Illustrative address</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>p.10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -10058,29 +10834,29 @@
       <c r="F43" s="12" t="n"/>
       <c r="G43" s="22" t="inlineStr">
         <is>
-          <t>Number of Stories 1 &amp; 2</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-10-06.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="24" t="inlineStr">
         <is>
-          <t>summary.tax_area_code</t>
+          <t>summary.structure</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>1 &amp; 2 stories</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>p.10</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -10091,29 +10867,29 @@
       <c r="F44" s="12" t="n"/>
       <c r="G44" s="22" t="inlineStr">
         <is>
-          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
+          <t>Number of Stories 1 &amp; 2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="24" t="inlineStr">
         <is>
-          <t>summary.tax_basis_label</t>
+          <t>summary.tax_area_code</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Limited property value (LPV), per the county assessor</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Vendored county rate table</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>property_tax_table.STATE_RULES['AZ']</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -10124,19 +10900,19 @@
       <c r="F45" s="12" t="n"/>
       <c r="G45" s="22" t="inlineStr">
         <is>
-          <t>What the assessed basis is in this state.</t>
+          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="24" t="inlineStr">
         <is>
-          <t>summary.tax_basis_note</t>
+          <t>summary.tax_basis_label</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Arizona taxes the limited property value, not the price. Under Proposition 117 (Ariz. C…</t>
+          <t>Limited property value (LPV), per the county assessor</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -10157,29 +10933,29 @@
       <c r="F46" s="12" t="n"/>
       <c r="G46" s="22" t="inlineStr">
         <is>
-          <t>How the basis behaves on a sale, with the authority.</t>
+          <t>What the assessed basis is in this state.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="24" t="inlineStr">
         <is>
-          <t>summary.tax_billed_amount</t>
+          <t>summary.tax_basis_note</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>249,122</t>
+          <t>Arizona taxes the limited property value, not the price. Under Proposition 117 (Ariz. C…</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
+          <t>Vendored county rate table</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>p.10</t>
+          <t>property_tax_table.STATE_RULES['AZ']</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -10190,19 +10966,19 @@
       <c r="F47" s="12" t="n"/>
       <c r="G47" s="22" t="inlineStr">
         <is>
-          <t>2025 Property Tax $249,122</t>
+          <t>How the basis behaves on a sale, with the authority.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="24" t="inlineStr">
         <is>
-          <t>summary.tax_billed_year</t>
+          <t>summary.tax_billed_amount</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>2,025</t>
+          <t>249,122</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
@@ -10230,22 +11006,22 @@
     <row r="49">
       <c r="A49" s="24" t="inlineStr">
         <is>
-          <t>summary.tax_divisor</t>
+          <t>summary.tax_billed_year</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>2,025</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Vendored county rate table</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>property_tax_table.STATE_RULES['AZ']</t>
+          <t>p.10</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -10256,29 +11032,29 @@
       <c r="F49" s="12" t="n"/>
       <c r="G49" s="22" t="inlineStr">
         <is>
-          <t>The rate's unit in Arizona: per $100 of assessed value.</t>
+          <t>2025 Property Tax $249,122</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="24" t="inlineStr">
         <is>
-          <t>summary.tax_exemption</t>
+          <t>summary.tax_divisor</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Vendored county rate table</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>property_tax_table.STATE_RULES['AZ']</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -10289,29 +11065,29 @@
       <c r="F50" s="12" t="n"/>
       <c r="G50" s="22" t="inlineStr">
         <is>
-          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
+          <t>The rate's unit in Arizona: per $100 of assessed value.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="24" t="inlineStr">
         <is>
-          <t>summary.tax_parcel_id</t>
+          <t>summary.tax_exemption</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>301-04-002K</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>p.10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -10322,56 +11098,52 @@
       <c r="F51" s="12" t="n"/>
       <c r="G51" s="22" t="inlineStr">
         <is>
-          <t>Tax Parcel Number 301-04-002K</t>
+          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="24" t="inlineStr">
         <is>
-          <t>summary.tax_per_unit_flag</t>
+          <t>summary.tax_parcel_id</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>In band (the statement's line per unit): $717 per unit a year is inside the AZ band of …</t>
+          <t>301-04-002K</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Vendored county rate table</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>property_tax_table.band_check</t>
+          <t>p.10</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>summary.tax_statement_amount, summary.unit_count, summary.state</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F52" s="12" t="n"/>
       <c r="G52" s="22" t="inlineStr">
         <is>
-          <t>A sanity check against the state's typical per-unit range. It flags; it never changes a figure.</t>
+          <t>Tax Parcel Number 301-04-002K</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="24" t="inlineStr">
         <is>
-          <t>summary.tax_rate_as_billed</t>
+          <t>summary.tax_per_unit_flag</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>10.26</t>
+          <t>In band (the statement's line per unit): $717 per unit a year is inside the AZ band of …</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -10381,30 +11153,34 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>property_tax_table.COUNTY_RATES[('AZ', 'maricopa')]</t>
+          <t>property_tax_table.band_check</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F53" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>summary.tax_statement_amount, summary.unit_count, summary.state</t>
+        </is>
+      </c>
       <c r="G53" s="22" t="inlineStr">
         <is>
-          <t>Tax area code 971300 — City of Phoenix / Deer Valley Unified School District #97, tax year 2025. Maricopa County, '2025 Tax Rates, Maricopa County, Arizona' (the treasurer's rate table by tax area code), row 971300: primary 6.7007, approx residential primary 5.1401, secondary 3.5566. Verified 2026-09-04.</t>
+          <t>A sanity check against the state's typical per-unit range. It flags; it never changes a figure.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="24" t="inlineStr">
         <is>
-          <t>summary.tax_rate_evidence</t>
+          <t>summary.tax_rate_as_billed</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Vendored county rate table: 10.2573 per $100 of assessed value, tax year 2025 — Tax are…</t>
+          <t>10.26</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
@@ -10414,34 +11190,30 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>property_tax_table.evidence_text</t>
+          <t>property_tax_table.COUNTY_RATES[('AZ', 'maricopa')]</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>summary.state, summary.county, summary.tax_parcel_id, summary.tax_billed_amount, summary.tax_billed_year</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F54" s="12" t="n"/>
       <c r="G54" s="22" t="inlineStr">
         <is>
-          <t>The citation, tax year and jurisdiction stack behind the rate, or the honest note that none is on file. Also records what the uploaded document stated for the field(s) it cites.</t>
+          <t>Tax area code 971300 — City of Phoenix / Deer Valley Unified School District #97, tax year 2025. Maricopa County, '2025 Tax Rates, Maricopa County, Arizona' (the treasurer's rate table by tax area code), row 971300: primary 6.7007, approx residential primary 5.1401, secondary 3.5566. Verified 2026-09-04.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="24" t="inlineStr">
         <is>
-          <t>summary.tax_rate_year</t>
+          <t>summary.tax_rate_evidence</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>2,025</t>
+          <t>Vendored county rate table: 10.2573 per $100 of assessed value, tax year 2025 — Tax are…</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -10451,147 +11223,151 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>property_tax_table.COUNTY_RATES[('AZ', 'maricopa')]</t>
+          <t>property_tax_table.evidence_text</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F55" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>summary.state, summary.county, summary.tax_parcel_id, summary.tax_billed_amount, summary.tax_billed_year</t>
+        </is>
+      </c>
       <c r="G55" s="22" t="inlineStr">
         <is>
-          <t>The tax year of the rate on file. A bill from another year is displayed, not tied out.</t>
+          <t>The citation, tax year and jurisdiction stack behind the rate, or the honest note that none is on file. Also records what the uploaded document stated for the field(s) it cites.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="24" t="inlineStr">
         <is>
-          <t>summary.tax_statement_amount</t>
+          <t>summary.tax_rate_year</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>239,566.79</t>
+          <t>2,025</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Sample Property T-12 June 26.xlsx</t>
+          <t>Vendored county rate table</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Property Taxes lines</t>
+          <t>property_tax_table.COUNTY_RATES[('AZ', 'maricopa')]</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>computed</t>
-        </is>
-      </c>
-      <c r="F56" s="5" t="inlineStr">
-        <is>
-          <t>t12.rows</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F56" s="12" t="n"/>
       <c r="G56" s="22" t="inlineStr">
         <is>
-          <t>The statement's lines categorised as Property Taxes, summed over its twelve months. As billed in the statement, not the county's bill.</t>
+          <t>The tax year of the rate on file. A bill from another year is displayed, not tied out.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="24" t="inlineStr">
         <is>
-          <t>summary.unit_count</t>
+          <t>summary.tax_statement_amount</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>239,566.79</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Sample Property RR 8.4.26.xlsx</t>
+          <t>Sample Property T-12 June 26.xlsx</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Property Taxes lines</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>computed</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>rent_roll.units</t>
+          <t>t12.rows</t>
         </is>
       </c>
       <c r="G57" s="22" t="inlineStr">
         <is>
-          <t>Counted from the rows of the uploaded rent roll.</t>
+          <t>The statement's lines categorised as Property Taxes, summed over its twelve months. As billed in the statement, not the county's bill.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="24" t="inlineStr">
         <is>
-          <t>summary.year_built</t>
+          <t>summary.unit_count</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>1,981</t>
+          <t>334</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
+          <t>Sample Property RR 8.4.26.xlsx</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>p.10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F58" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>rent_roll.units</t>
+        </is>
+      </c>
       <c r="G58" s="22" t="inlineStr">
         <is>
-          <t>Y ear Built 1981</t>
+          <t>Counted from the rows of the uploaded rent roll.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="24" t="inlineStr">
         <is>
-          <t>summary.zip</t>
+          <t>summary.year_built</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>85204</t>
+          <t>1,981</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Illustrative address</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>p.10</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -10602,75 +11378,108 @@
       <c r="F59" s="12" t="n"/>
       <c r="G59" s="22" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
+          <t>Y ear Built 1981</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="24" t="inlineStr">
         <is>
-          <t>supply.projects</t>
+          <t>summary.zip</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>32 entries</t>
+          <t>85204</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Public permit and entitlement records (the operator's supply pipeline), via the market-report service</t>
+          <t>Illustrative address</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>POST /report (format json)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F60" s="5" t="inlineStr">
-        <is>
-          <t>supply.rings</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F60" s="12" t="n"/>
       <c r="G60" s="22" t="inlineStr">
         <is>
-          <t>The developments the counts are made of, within 3 mi: one row per development, reconciled across the pipeline's lifecycle layers and shown at the furthest stage any layer carries.</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-10-06.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="24" t="inlineStr">
         <is>
+          <t>supply.projects</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>33 entries</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>Public permit and entitlement records (the operator's supply pipeline), via the market-report service</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>POST /report (format json)</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
           <t>supply.rings</t>
         </is>
       </c>
-      <c r="B61" s="5" t="inlineStr">
+      <c r="G61" s="22" t="inlineStr">
+        <is>
+          <t>The developments the counts are made of, within 3 mi: one row per development, reconciled across the pipeline's lifecycle layers and shown at the furthest stage any layer carries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="24" t="inlineStr">
+        <is>
+          <t>supply.rings</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
         <is>
           <t>8 entries</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
         <is>
           <t>Public permit and entitlement records (the operator's supply pipeline), via the market-report service</t>
         </is>
       </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="D62" s="5" t="inlineStr">
         <is>
           <t>POST /report (format json)</t>
         </is>
       </c>
-      <c r="E61" s="5" t="inlineStr">
+      <c r="E62" s="5" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="F61" s="12" t="n"/>
-      <c r="G61" s="22" t="inlineStr">
+      <c r="F62" s="12" t="n"/>
+      <c r="G62" s="22" t="inlineStr">
         <is>
           <t>Projects and units by cumulative ring and tracked stage, counted from the service's project rows.</t>
         </is>
